--- a/assignments/식용작물학1_감자_분석.xlsx
+++ b/assignments/식용작물학1_감자_분석.xlsx
@@ -18,8 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0&quot;년&quot;"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -85,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -103,7 +104,13 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -207,6 +214,12 @@
           <tx>
             <strRef>
               <f>'분석'!B4</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>재배면적(ha)</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -226,11 +239,139 @@
           <cat>
             <numRef>
               <f>'분석'!$A$5:$A$24</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="20"/>
+                <pt idx="0">
+                  <v>2005</v>
+                </pt>
+                <pt idx="1">
+                  <v>2006</v>
+                </pt>
+                <pt idx="2">
+                  <v>2007</v>
+                </pt>
+                <pt idx="3">
+                  <v>2008</v>
+                </pt>
+                <pt idx="4">
+                  <v>2009</v>
+                </pt>
+                <pt idx="5">
+                  <v>2010</v>
+                </pt>
+                <pt idx="6">
+                  <v>2011</v>
+                </pt>
+                <pt idx="7">
+                  <v>2012</v>
+                </pt>
+                <pt idx="8">
+                  <v>2013</v>
+                </pt>
+                <pt idx="9">
+                  <v>2014</v>
+                </pt>
+                <pt idx="10">
+                  <v>2015</v>
+                </pt>
+                <pt idx="11">
+                  <v>2016</v>
+                </pt>
+                <pt idx="12">
+                  <v>2017</v>
+                </pt>
+                <pt idx="13">
+                  <v>2018</v>
+                </pt>
+                <pt idx="14">
+                  <v>2019</v>
+                </pt>
+                <pt idx="15">
+                  <v>2020</v>
+                </pt>
+                <pt idx="16">
+                  <v>2021</v>
+                </pt>
+                <pt idx="17">
+                  <v>2022</v>
+                </pt>
+                <pt idx="18">
+                  <v>2023</v>
+                </pt>
+                <pt idx="19">
+                  <v>2024</v>
+                </pt>
+              </numCache>
             </numRef>
           </cat>
           <val>
             <numRef>
               <f>'분석'!$B$5:$B$24</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="20"/>
+                <pt idx="0">
+                  <v>32728</v>
+                </pt>
+                <pt idx="1">
+                  <v>23957</v>
+                </pt>
+                <pt idx="2">
+                  <v>20421</v>
+                </pt>
+                <pt idx="3">
+                  <v>20540</v>
+                </pt>
+                <pt idx="4">
+                  <v>21396</v>
+                </pt>
+                <pt idx="5">
+                  <v>24913</v>
+                </pt>
+                <pt idx="6">
+                  <v>26804</v>
+                </pt>
+                <pt idx="7">
+                  <v>24930</v>
+                </pt>
+                <pt idx="8">
+                  <v>27430</v>
+                </pt>
+                <pt idx="9">
+                  <v>21472</v>
+                </pt>
+                <pt idx="10">
+                  <v>20234</v>
+                </pt>
+                <pt idx="11">
+                  <v>22000</v>
+                </pt>
+                <pt idx="12">
+                  <v>20974</v>
+                </pt>
+                <pt idx="13">
+                  <v>23402</v>
+                </pt>
+                <pt idx="14">
+                  <v>26829</v>
+                </pt>
+                <pt idx="15">
+                  <v>23599</v>
+                </pt>
+                <pt idx="16">
+                  <v>21745</v>
+                </pt>
+                <pt idx="17">
+                  <v>20088</v>
+                </pt>
+                <pt idx="18">
+                  <v>22525</v>
+                </pt>
+                <pt idx="19">
+                  <v>23969</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -329,6 +470,12 @@
           <tx>
             <strRef>
               <f>'분석'!C4</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>단수(kg/10a)</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -348,11 +495,139 @@
           <cat>
             <numRef>
               <f>'분석'!$A$5:$A$24</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="20"/>
+                <pt idx="0">
+                  <v>2005</v>
+                </pt>
+                <pt idx="1">
+                  <v>2006</v>
+                </pt>
+                <pt idx="2">
+                  <v>2007</v>
+                </pt>
+                <pt idx="3">
+                  <v>2008</v>
+                </pt>
+                <pt idx="4">
+                  <v>2009</v>
+                </pt>
+                <pt idx="5">
+                  <v>2010</v>
+                </pt>
+                <pt idx="6">
+                  <v>2011</v>
+                </pt>
+                <pt idx="7">
+                  <v>2012</v>
+                </pt>
+                <pt idx="8">
+                  <v>2013</v>
+                </pt>
+                <pt idx="9">
+                  <v>2014</v>
+                </pt>
+                <pt idx="10">
+                  <v>2015</v>
+                </pt>
+                <pt idx="11">
+                  <v>2016</v>
+                </pt>
+                <pt idx="12">
+                  <v>2017</v>
+                </pt>
+                <pt idx="13">
+                  <v>2018</v>
+                </pt>
+                <pt idx="14">
+                  <v>2019</v>
+                </pt>
+                <pt idx="15">
+                  <v>2020</v>
+                </pt>
+                <pt idx="16">
+                  <v>2021</v>
+                </pt>
+                <pt idx="17">
+                  <v>2022</v>
+                </pt>
+                <pt idx="18">
+                  <v>2023</v>
+                </pt>
+                <pt idx="19">
+                  <v>2024</v>
+                </pt>
+              </numCache>
             </numRef>
           </cat>
           <val>
             <numRef>
               <f>'분석'!$C$5:$C$24</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="20"/>
+                <pt idx="0">
+                  <v>2732</v>
+                </pt>
+                <pt idx="1">
+                  <v>2634</v>
+                </pt>
+                <pt idx="2">
+                  <v>2813</v>
+                </pt>
+                <pt idx="3">
+                  <v>2943</v>
+                </pt>
+                <pt idx="4">
+                  <v>2762</v>
+                </pt>
+                <pt idx="5">
+                  <v>2475</v>
+                </pt>
+                <pt idx="6">
+                  <v>2321</v>
+                </pt>
+                <pt idx="7">
+                  <v>2437</v>
+                </pt>
+                <pt idx="8">
+                  <v>2652</v>
+                </pt>
+                <pt idx="9">
+                  <v>2750</v>
+                </pt>
+                <pt idx="10">
+                  <v>2658</v>
+                </pt>
+                <pt idx="11">
+                  <v>2526</v>
+                </pt>
+                <pt idx="12">
+                  <v>2225</v>
+                </pt>
+                <pt idx="13">
+                  <v>2342</v>
+                </pt>
+                <pt idx="14">
+                  <v>2573</v>
+                </pt>
+                <pt idx="15">
+                  <v>2344</v>
+                </pt>
+                <pt idx="16">
+                  <v>2552</v>
+                </pt>
+                <pt idx="17">
+                  <v>2392</v>
+                </pt>
+                <pt idx="18">
+                  <v>2443</v>
+                </pt>
+                <pt idx="19">
+                  <v>2474</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -451,6 +726,13 @@
           <tx>
             <strRef>
               <f>'분석'!E4</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>재배면적 지수
+(2005=100)</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -470,11 +752,139 @@
           <cat>
             <numRef>
               <f>'분석'!$A$5:$A$24</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="20"/>
+                <pt idx="0">
+                  <v>2005</v>
+                </pt>
+                <pt idx="1">
+                  <v>2006</v>
+                </pt>
+                <pt idx="2">
+                  <v>2007</v>
+                </pt>
+                <pt idx="3">
+                  <v>2008</v>
+                </pt>
+                <pt idx="4">
+                  <v>2009</v>
+                </pt>
+                <pt idx="5">
+                  <v>2010</v>
+                </pt>
+                <pt idx="6">
+                  <v>2011</v>
+                </pt>
+                <pt idx="7">
+                  <v>2012</v>
+                </pt>
+                <pt idx="8">
+                  <v>2013</v>
+                </pt>
+                <pt idx="9">
+                  <v>2014</v>
+                </pt>
+                <pt idx="10">
+                  <v>2015</v>
+                </pt>
+                <pt idx="11">
+                  <v>2016</v>
+                </pt>
+                <pt idx="12">
+                  <v>2017</v>
+                </pt>
+                <pt idx="13">
+                  <v>2018</v>
+                </pt>
+                <pt idx="14">
+                  <v>2019</v>
+                </pt>
+                <pt idx="15">
+                  <v>2020</v>
+                </pt>
+                <pt idx="16">
+                  <v>2021</v>
+                </pt>
+                <pt idx="17">
+                  <v>2022</v>
+                </pt>
+                <pt idx="18">
+                  <v>2023</v>
+                </pt>
+                <pt idx="19">
+                  <v>2024</v>
+                </pt>
+              </numCache>
             </numRef>
           </cat>
           <val>
             <numRef>
               <f>'분석'!$E$5:$E$24</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="20"/>
+                <pt idx="0">
+                  <v>100</v>
+                </pt>
+                <pt idx="1">
+                  <v>73.2003177707162</v>
+                </pt>
+                <pt idx="2">
+                  <v>62.3961134197018</v>
+                </pt>
+                <pt idx="3">
+                  <v>62.7597164507455</v>
+                </pt>
+                <pt idx="4">
+                  <v>65.3752138841359</v>
+                </pt>
+                <pt idx="5">
+                  <v>76.1213639696896</v>
+                </pt>
+                <pt idx="6">
+                  <v>81.8992911268638</v>
+                </pt>
+                <pt idx="7">
+                  <v>76.1733072598387</v>
+                </pt>
+                <pt idx="8">
+                  <v>83.8120263994133</v>
+                </pt>
+                <pt idx="9">
+                  <v>65.607430945979</v>
+                </pt>
+                <pt idx="10">
+                  <v>61.8247372280616</v>
+                </pt>
+                <pt idx="11">
+                  <v>67.2207284282572</v>
+                </pt>
+                <pt idx="12">
+                  <v>64.0857980933757</v>
+                </pt>
+                <pt idx="13">
+                  <v>71.5045221217306</v>
+                </pt>
+                <pt idx="14">
+                  <v>81.9756783182596</v>
+                </pt>
+                <pt idx="15">
+                  <v>72.1064531899291</v>
+                </pt>
+                <pt idx="16">
+                  <v>66.4415790760205</v>
+                </pt>
+                <pt idx="17">
+                  <v>61.3786360303104</v>
+                </pt>
+                <pt idx="18">
+                  <v>68.8248594475678</v>
+                </pt>
+                <pt idx="19">
+                  <v>73.2369836225862</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -485,6 +895,13 @@
           <tx>
             <strRef>
               <f>'분석'!F4</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>단수 지수
+(2005=100)</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -504,11 +921,139 @@
           <cat>
             <numRef>
               <f>'분석'!$A$5:$A$24</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="20"/>
+                <pt idx="0">
+                  <v>2005</v>
+                </pt>
+                <pt idx="1">
+                  <v>2006</v>
+                </pt>
+                <pt idx="2">
+                  <v>2007</v>
+                </pt>
+                <pt idx="3">
+                  <v>2008</v>
+                </pt>
+                <pt idx="4">
+                  <v>2009</v>
+                </pt>
+                <pt idx="5">
+                  <v>2010</v>
+                </pt>
+                <pt idx="6">
+                  <v>2011</v>
+                </pt>
+                <pt idx="7">
+                  <v>2012</v>
+                </pt>
+                <pt idx="8">
+                  <v>2013</v>
+                </pt>
+                <pt idx="9">
+                  <v>2014</v>
+                </pt>
+                <pt idx="10">
+                  <v>2015</v>
+                </pt>
+                <pt idx="11">
+                  <v>2016</v>
+                </pt>
+                <pt idx="12">
+                  <v>2017</v>
+                </pt>
+                <pt idx="13">
+                  <v>2018</v>
+                </pt>
+                <pt idx="14">
+                  <v>2019</v>
+                </pt>
+                <pt idx="15">
+                  <v>2020</v>
+                </pt>
+                <pt idx="16">
+                  <v>2021</v>
+                </pt>
+                <pt idx="17">
+                  <v>2022</v>
+                </pt>
+                <pt idx="18">
+                  <v>2023</v>
+                </pt>
+                <pt idx="19">
+                  <v>2024</v>
+                </pt>
+              </numCache>
             </numRef>
           </cat>
           <val>
             <numRef>
               <f>'분석'!$F$5:$F$24</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="20"/>
+                <pt idx="0">
+                  <v>100</v>
+                </pt>
+                <pt idx="1">
+                  <v>96.4128843338214</v>
+                </pt>
+                <pt idx="2">
+                  <v>102.96486090776</v>
+                </pt>
+                <pt idx="3">
+                  <v>107.723279648609</v>
+                </pt>
+                <pt idx="4">
+                  <v>101.098096632504</v>
+                </pt>
+                <pt idx="5">
+                  <v>90.592972181552</v>
+                </pt>
+                <pt idx="6">
+                  <v>84.9560761346999</v>
+                </pt>
+                <pt idx="7">
+                  <v>89.2020497803807</v>
+                </pt>
+                <pt idx="8">
+                  <v>97.0717423133236</v>
+                </pt>
+                <pt idx="9">
+                  <v>100.658857979502</v>
+                </pt>
+                <pt idx="10">
+                  <v>97.2913616398243</v>
+                </pt>
+                <pt idx="11">
+                  <v>92.4597364568082</v>
+                </pt>
+                <pt idx="12">
+                  <v>81.4421669106881</v>
+                </pt>
+                <pt idx="13">
+                  <v>85.7247437774524</v>
+                </pt>
+                <pt idx="14">
+                  <v>94.1800878477306</v>
+                </pt>
+                <pt idx="15">
+                  <v>85.7979502196193</v>
+                </pt>
+                <pt idx="16">
+                  <v>93.411420204978</v>
+                </pt>
+                <pt idx="17">
+                  <v>87.5549048316252</v>
+                </pt>
+                <pt idx="18">
+                  <v>89.4216691068814</v>
+                </pt>
+                <pt idx="19">
+                  <v>90.5563689604685</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -519,6 +1064,13 @@
           <tx>
             <strRef>
               <f>'분석'!G4</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>생산량 지수
+(2005=100)</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
@@ -538,11 +1090,139 @@
           <cat>
             <numRef>
               <f>'분석'!$A$5:$A$24</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="20"/>
+                <pt idx="0">
+                  <v>2005</v>
+                </pt>
+                <pt idx="1">
+                  <v>2006</v>
+                </pt>
+                <pt idx="2">
+                  <v>2007</v>
+                </pt>
+                <pt idx="3">
+                  <v>2008</v>
+                </pt>
+                <pt idx="4">
+                  <v>2009</v>
+                </pt>
+                <pt idx="5">
+                  <v>2010</v>
+                </pt>
+                <pt idx="6">
+                  <v>2011</v>
+                </pt>
+                <pt idx="7">
+                  <v>2012</v>
+                </pt>
+                <pt idx="8">
+                  <v>2013</v>
+                </pt>
+                <pt idx="9">
+                  <v>2014</v>
+                </pt>
+                <pt idx="10">
+                  <v>2015</v>
+                </pt>
+                <pt idx="11">
+                  <v>2016</v>
+                </pt>
+                <pt idx="12">
+                  <v>2017</v>
+                </pt>
+                <pt idx="13">
+                  <v>2018</v>
+                </pt>
+                <pt idx="14">
+                  <v>2019</v>
+                </pt>
+                <pt idx="15">
+                  <v>2020</v>
+                </pt>
+                <pt idx="16">
+                  <v>2021</v>
+                </pt>
+                <pt idx="17">
+                  <v>2022</v>
+                </pt>
+                <pt idx="18">
+                  <v>2023</v>
+                </pt>
+                <pt idx="19">
+                  <v>2024</v>
+                </pt>
+              </numCache>
             </numRef>
           </cat>
           <val>
             <numRef>
               <f>'분석'!$G$5:$G$24</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="20"/>
+                <pt idx="0">
+                  <v>100</v>
+                </pt>
+                <pt idx="1">
+                  <v>70.574302600605</v>
+                </pt>
+                <pt idx="2">
+                  <v>64.2346639231057</v>
+                </pt>
+                <pt idx="3">
+                  <v>67.6114804605157</v>
+                </pt>
+                <pt idx="4">
+                  <v>66.0974150511901</v>
+                </pt>
+                <pt idx="5">
+                  <v>68.9663000508826</v>
+                </pt>
+                <pt idx="6">
+                  <v>69.5808055109789</v>
+                </pt>
+                <pt idx="7">
+                  <v>67.9404841117628</v>
+                </pt>
+                <pt idx="8">
+                  <v>81.3493399238438</v>
+                </pt>
+                <pt idx="9">
+                  <v>66.0391516581583</v>
+                </pt>
+                <pt idx="10">
+                  <v>60.1352023842141</v>
+                </pt>
+                <pt idx="11">
+                  <v>62.1405366718295</v>
+                </pt>
+                <pt idx="12">
+                  <v>52.1971785308902</v>
+                </pt>
+                <pt idx="13">
+                  <v>61.2900700614505</v>
+                </pt>
+                <pt idx="14">
+                  <v>77.2095077805673</v>
+                </pt>
+                <pt idx="15">
+                  <v>61.8636457675168</v>
+                </pt>
+                <pt idx="16">
+                  <v>62.0536448169624</v>
+                </pt>
+                <pt idx="17">
+                  <v>53.7455757284322</v>
+                </pt>
+                <pt idx="18">
+                  <v>61.5392271433604</v>
+                </pt>
+                <pt idx="19">
+                  <v>66.3170490318324</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -618,7 +1298,7 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>7</col>
+      <col>8</col>
       <colOff>0</colOff>
       <row>0</row>
       <rowOff>0</rowOff>
@@ -640,7 +1320,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>7</col>
+      <col>8</col>
       <colOff>0</colOff>
       <row>16</row>
       <rowOff>0</rowOff>
@@ -662,7 +1342,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>7</col>
+      <col>8</col>
       <colOff>0</colOff>
       <row>32</row>
       <rowOff>0</rowOff>
@@ -27752,7 +28432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R24"/>
+  <dimension ref="A1:R26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -27902,27 +28582,27 @@
       </c>
       <c r="B5" s="5">
         <f>'Raw data'!H3</f>
-        <v/>
+        <v>32728</v>
       </c>
       <c r="C5" s="5">
         <f>'Raw data'!I3</f>
-        <v/>
+        <v>2732</v>
       </c>
       <c r="D5" s="5">
         <f>'Raw data'!J3</f>
-        <v/>
+        <v>894215</v>
       </c>
       <c r="E5" s="6">
         <f>IF(B5="","",B5/B$5*100)</f>
-        <v/>
+        <v>100</v>
       </c>
       <c r="F5" s="6">
         <f>IF(C5="","",C5/C$5*100)</f>
-        <v/>
+        <v>100</v>
       </c>
       <c r="G5" s="6">
         <f>IF(D5="","",D5/D$5*100)</f>
-        <v/>
+        <v>100</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
@@ -27941,31 +28621,31 @@
       </c>
       <c r="L5" s="5">
         <f>'Raw data'!K3</f>
-        <v/>
+        <v>20035</v>
       </c>
       <c r="M5" s="5">
         <f>'Raw data'!N3</f>
-        <v/>
+        <v>4385</v>
       </c>
       <c r="N5" s="5">
         <f>'Raw data'!Q3</f>
-        <v/>
+        <v>8308</v>
       </c>
       <c r="O5" s="5">
         <f>'Raw data'!L3</f>
-        <v/>
+        <v>2767</v>
       </c>
       <c r="P5" s="5">
         <f>'Raw data'!O3</f>
-        <v/>
+        <v>3517</v>
       </c>
       <c r="Q5" s="5">
         <f>'Raw data'!R3</f>
-        <v/>
+        <v>2233</v>
       </c>
       <c r="R5" s="5">
         <f>'Raw data'!H21</f>
-        <v/>
+        <v>6174</v>
       </c>
     </row>
     <row r="6">
@@ -27974,67 +28654,67 @@
       </c>
       <c r="B6" s="5">
         <f>'Raw data'!Y3</f>
-        <v/>
+        <v>23957</v>
       </c>
       <c r="C6" s="5">
         <f>'Raw data'!Z3</f>
-        <v/>
+        <v>2634</v>
       </c>
       <c r="D6" s="5">
         <f>'Raw data'!AA3</f>
-        <v/>
+        <v>631086</v>
       </c>
       <c r="E6" s="6">
         <f>IF(B6="","",B6/B$5*100)</f>
-        <v/>
+        <v>73.2003177707162</v>
       </c>
       <c r="F6" s="6">
         <f>IF(C6="","",C6/C$5*100)</f>
-        <v/>
+        <v>96.4128843338214</v>
       </c>
       <c r="G6" s="6">
         <f>IF(D6="","",D6/D$5*100)</f>
-        <v/>
+        <v>70.574302600605</v>
       </c>
       <c r="H6" s="6">
         <f>IF(OR(D6="",D5=""),"",(D6-D5)/D5*100)</f>
-        <v/>
+        <v>-29.425697399395</v>
       </c>
       <c r="I6" s="6">
         <f>IF(OR(B6="",B5=""),"",(B6-B5)/B5*100)</f>
-        <v/>
+        <v>-26.7996822292838</v>
       </c>
       <c r="J6" s="6">
         <f>IF(OR(C6="",C5=""),"",(C6-C5)/C5*100)</f>
-        <v/>
+        <v>-3.58711566617862</v>
       </c>
       <c r="L6" s="5">
         <f>'Raw data'!AB3</f>
-        <v/>
+        <v>14960</v>
       </c>
       <c r="M6" s="5">
         <f>'Raw data'!AE3</f>
-        <v/>
+        <v>3971</v>
       </c>
       <c r="N6" s="5">
         <f>'Raw data'!AH3</f>
-        <v/>
+        <v>5026</v>
       </c>
       <c r="O6" s="5">
         <f>'Raw data'!AC3</f>
-        <v/>
+        <v>2799</v>
       </c>
       <c r="P6" s="5">
         <f>'Raw data'!AF3</f>
-        <v/>
+        <v>2404</v>
       </c>
       <c r="Q6" s="5">
         <f>'Raw data'!AI3</f>
-        <v/>
+        <v>2328</v>
       </c>
       <c r="R6" s="5">
         <f>'Raw data'!Y21</f>
-        <v/>
+        <v>4167</v>
       </c>
     </row>
     <row r="7">
@@ -28043,67 +28723,67 @@
       </c>
       <c r="B7" s="5">
         <f>'Raw data'!AP3</f>
-        <v/>
+        <v>20421</v>
       </c>
       <c r="C7" s="5">
         <f>'Raw data'!AQ3</f>
-        <v/>
+        <v>2813</v>
       </c>
       <c r="D7" s="5">
         <f>'Raw data'!AR3</f>
-        <v/>
+        <v>574396</v>
       </c>
       <c r="E7" s="6">
         <f>IF(B7="","",B7/B$5*100)</f>
-        <v/>
+        <v>62.3961134197018</v>
       </c>
       <c r="F7" s="6">
         <f>IF(C7="","",C7/C$5*100)</f>
-        <v/>
+        <v>102.96486090776</v>
       </c>
       <c r="G7" s="6">
         <f>IF(D7="","",D7/D$5*100)</f>
-        <v/>
+        <v>64.2346639231057</v>
       </c>
       <c r="H7" s="6">
         <f>IF(OR(D7="",D6=""),"",(D7-D6)/D6*100)</f>
-        <v/>
+        <v>-8.98292784184723</v>
       </c>
       <c r="I7" s="6">
         <f>IF(OR(B7="",B6=""),"",(B7-B6)/B6*100)</f>
-        <v/>
+        <v>-14.7597779354677</v>
       </c>
       <c r="J7" s="6">
         <f>IF(OR(C7="",C6=""),"",(C7-C6)/C6*100)</f>
-        <v/>
+        <v>6.79574791192103</v>
       </c>
       <c r="L7" s="5">
         <f>'Raw data'!AS3</f>
-        <v/>
+        <v>13033</v>
       </c>
       <c r="M7" s="5">
         <f>'Raw data'!AV3</f>
-        <v/>
+        <v>3202</v>
       </c>
       <c r="N7" s="5">
         <f>'Raw data'!AY3</f>
-        <v/>
+        <v>4186</v>
       </c>
       <c r="O7" s="5">
         <f>'Raw data'!AT3</f>
-        <v/>
+        <v>2818</v>
       </c>
       <c r="P7" s="5">
         <f>'Raw data'!AW3</f>
-        <v/>
+        <v>3516</v>
       </c>
       <c r="Q7" s="5">
         <f>'Raw data'!AZ3</f>
-        <v/>
+        <v>2259</v>
       </c>
       <c r="R7" s="5">
         <f>'Raw data'!AP21</f>
-        <v/>
+        <v>2717</v>
       </c>
     </row>
     <row r="8">
@@ -28112,67 +28792,67 @@
       </c>
       <c r="B8" s="5">
         <f>'Raw data'!BG3</f>
-        <v/>
+        <v>20540</v>
       </c>
       <c r="C8" s="5">
         <f>'Raw data'!BH3</f>
-        <v/>
+        <v>2943</v>
       </c>
       <c r="D8" s="5">
         <f>'Raw data'!BI3</f>
-        <v/>
+        <v>604592</v>
       </c>
       <c r="E8" s="6">
         <f>IF(B8="","",B8/B$5*100)</f>
-        <v/>
+        <v>62.7597164507455</v>
       </c>
       <c r="F8" s="6">
         <f>IF(C8="","",C8/C$5*100)</f>
-        <v/>
+        <v>107.723279648609</v>
       </c>
       <c r="G8" s="6">
         <f>IF(D8="","",D8/D$5*100)</f>
-        <v/>
+        <v>67.6114804605157</v>
       </c>
       <c r="H8" s="6">
         <f>IF(OR(D8="",D7=""),"",(D8-D7)/D7*100)</f>
-        <v/>
+        <v>5.2570003969387</v>
       </c>
       <c r="I8" s="6">
         <f>IF(OR(B8="",B7=""),"",(B8-B7)/B7*100)</f>
-        <v/>
+        <v>0.582733460653249</v>
       </c>
       <c r="J8" s="6">
         <f>IF(OR(C8="",C7=""),"",(C8-C7)/C7*100)</f>
-        <v/>
+        <v>4.62140063988624</v>
       </c>
       <c r="L8" s="5">
         <f>'Raw data'!BJ3</f>
-        <v/>
+        <v>13048</v>
       </c>
       <c r="M8" s="5">
         <f>'Raw data'!BM3</f>
-        <v/>
+        <v>3364</v>
       </c>
       <c r="N8" s="5">
         <f>'Raw data'!BP3</f>
-        <v/>
+        <v>4128</v>
       </c>
       <c r="O8" s="5">
         <f>'Raw data'!BK3</f>
-        <v/>
+        <v>2930</v>
       </c>
       <c r="P8" s="5">
         <f>'Raw data'!BN3</f>
-        <v/>
+        <v>3650</v>
       </c>
       <c r="Q8" s="5">
         <f>'Raw data'!BQ3</f>
-        <v/>
+        <v>2409</v>
       </c>
       <c r="R8" s="5">
         <f>'Raw data'!BG21</f>
-        <v/>
+        <v>2663</v>
       </c>
     </row>
     <row r="9">
@@ -28181,67 +28861,67 @@
       </c>
       <c r="B9" s="5">
         <f>'Raw data'!BX3</f>
-        <v/>
+        <v>21396</v>
       </c>
       <c r="C9" s="5">
         <f>'Raw data'!BY3</f>
-        <v/>
+        <v>2762</v>
       </c>
       <c r="D9" s="5">
         <f>'Raw data'!BZ3</f>
-        <v/>
+        <v>591053</v>
       </c>
       <c r="E9" s="6">
         <f>IF(B9="","",B9/B$5*100)</f>
-        <v/>
+        <v>65.3752138841359</v>
       </c>
       <c r="F9" s="6">
         <f>IF(C9="","",C9/C$5*100)</f>
-        <v/>
+        <v>101.098096632504</v>
       </c>
       <c r="G9" s="6">
         <f>IF(D9="","",D9/D$5*100)</f>
-        <v/>
+        <v>66.0974150511901</v>
       </c>
       <c r="H9" s="6">
         <f>IF(OR(D9="",D8=""),"",(D9-D8)/D8*100)</f>
-        <v/>
+        <v>-2.23936142059438</v>
       </c>
       <c r="I9" s="6">
         <f>IF(OR(B9="",B8=""),"",(B9-B8)/B8*100)</f>
-        <v/>
+        <v>4.16747809152872</v>
       </c>
       <c r="J9" s="6">
         <f>IF(OR(C9="",C8=""),"",(C9-C8)/C8*100)</f>
-        <v/>
+        <v>-6.15018688413184</v>
       </c>
       <c r="L9" s="5">
         <f>'Raw data'!CA3</f>
-        <v/>
+        <v>14198</v>
       </c>
       <c r="M9" s="5">
         <f>'Raw data'!CD3</f>
-        <v/>
+        <v>3322</v>
       </c>
       <c r="N9" s="5">
         <f>'Raw data'!CG3</f>
-        <v/>
+        <v>3876</v>
       </c>
       <c r="O9" s="5">
         <f>'Raw data'!CB3</f>
-        <v/>
+        <v>2778</v>
       </c>
       <c r="P9" s="5">
         <f>'Raw data'!CE3</f>
-        <v/>
+        <v>3487</v>
       </c>
       <c r="Q9" s="5">
         <f>'Raw data'!CH3</f>
-        <v/>
+        <v>2084</v>
       </c>
       <c r="R9" s="5">
         <f>'Raw data'!BX21</f>
-        <v/>
+        <v>2413</v>
       </c>
     </row>
     <row r="10">
@@ -28250,67 +28930,67 @@
       </c>
       <c r="B10" s="5">
         <f>'Raw data'!CO3</f>
-        <v/>
+        <v>24913</v>
       </c>
       <c r="C10" s="5">
         <f>'Raw data'!CP3</f>
-        <v/>
+        <v>2475</v>
       </c>
       <c r="D10" s="5">
         <f>'Raw data'!CQ3</f>
-        <v/>
+        <v>616707</v>
       </c>
       <c r="E10" s="6">
         <f>IF(B10="","",B10/B$5*100)</f>
-        <v/>
+        <v>76.1213639696896</v>
       </c>
       <c r="F10" s="6">
         <f>IF(C10="","",C10/C$5*100)</f>
-        <v/>
+        <v>90.592972181552</v>
       </c>
       <c r="G10" s="6">
         <f>IF(D10="","",D10/D$5*100)</f>
-        <v/>
+        <v>68.9663000508826</v>
       </c>
       <c r="H10" s="6">
         <f>IF(OR(D10="",D9=""),"",(D10-D9)/D9*100)</f>
-        <v/>
+        <v>4.34038910216174</v>
       </c>
       <c r="I10" s="6">
         <f>IF(OR(B10="",B9=""),"",(B10-B9)/B9*100)</f>
-        <v/>
+        <v>16.4376518975509</v>
       </c>
       <c r="J10" s="6">
         <f>IF(OR(C10="",C9=""),"",(C10-C9)/C9*100)</f>
-        <v/>
+        <v>-10.3910209992759</v>
       </c>
       <c r="L10" s="5">
         <f>'Raw data'!CR3</f>
-        <v/>
+        <v>16302</v>
       </c>
       <c r="M10" s="5">
         <f>'Raw data'!CU3</f>
-        <v/>
+        <v>3801</v>
       </c>
       <c r="N10" s="5">
         <f>'Raw data'!CX3</f>
-        <v/>
+        <v>4810</v>
       </c>
       <c r="O10" s="5">
         <f>'Raw data'!CS3</f>
-        <v/>
+        <v>2415</v>
       </c>
       <c r="P10" s="5">
         <f>'Raw data'!CV3</f>
-        <v/>
+        <v>3668</v>
       </c>
       <c r="Q10" s="5">
         <f>'Raw data'!CY3</f>
-        <v/>
+        <v>1739</v>
       </c>
       <c r="R10" s="5">
         <f>'Raw data'!CO21</f>
-        <v/>
+        <v>2766</v>
       </c>
     </row>
     <row r="11">
@@ -28319,67 +28999,67 @@
       </c>
       <c r="B11" s="5">
         <f>'Raw data'!DF3</f>
-        <v/>
+        <v>26804</v>
       </c>
       <c r="C11" s="5">
         <f>'Raw data'!DG3</f>
-        <v/>
+        <v>2321</v>
       </c>
       <c r="D11" s="5">
         <f>'Raw data'!DH3</f>
-        <v/>
+        <v>622202</v>
       </c>
       <c r="E11" s="6">
         <f>IF(B11="","",B11/B$5*100)</f>
-        <v/>
+        <v>81.8992911268638</v>
       </c>
       <c r="F11" s="6">
         <f>IF(C11="","",C11/C$5*100)</f>
-        <v/>
+        <v>84.9560761346999</v>
       </c>
       <c r="G11" s="6">
         <f>IF(D11="","",D11/D$5*100)</f>
-        <v/>
+        <v>69.5808055109789</v>
       </c>
       <c r="H11" s="6">
         <f>IF(OR(D11="",D10=""),"",(D11-D10)/D10*100)</f>
-        <v/>
+        <v>0.891022803373401</v>
       </c>
       <c r="I11" s="6">
         <f>IF(OR(B11="",B10=""),"",(B11-B10)/B10*100)</f>
-        <v/>
+        <v>7.59041464295749</v>
       </c>
       <c r="J11" s="6">
         <f>IF(OR(C11="",C10=""),"",(C11-C10)/C10*100)</f>
-        <v/>
+        <v>-6.22222222222222</v>
       </c>
       <c r="L11" s="5">
         <f>'Raw data'!DI3</f>
-        <v/>
+        <v>19126</v>
       </c>
       <c r="M11" s="5">
         <f>'Raw data'!DL3</f>
-        <v/>
+        <v>3784</v>
       </c>
       <c r="N11" s="5">
         <f>'Raw data'!DO3</f>
-        <v/>
+        <v>3894</v>
       </c>
       <c r="O11" s="5">
         <f>'Raw data'!DJ3</f>
-        <v/>
+        <v>2392</v>
       </c>
       <c r="P11" s="5">
         <f>'Raw data'!DM3</f>
-        <v/>
+        <v>2509</v>
       </c>
       <c r="Q11" s="5">
         <f>'Raw data'!DP3</f>
-        <v/>
+        <v>1789</v>
       </c>
       <c r="R11" s="5">
         <f>'Raw data'!DF21</f>
-        <v/>
+        <v>2814</v>
       </c>
     </row>
     <row r="12">
@@ -28388,67 +29068,67 @@
       </c>
       <c r="B12" s="5">
         <f>'Raw data'!DW3</f>
-        <v/>
+        <v>24930</v>
       </c>
       <c r="C12" s="5">
         <f>'Raw data'!DX3</f>
-        <v/>
+        <v>2437</v>
       </c>
       <c r="D12" s="5">
         <f>'Raw data'!DY3</f>
-        <v/>
+        <v>607534</v>
       </c>
       <c r="E12" s="6">
         <f>IF(B12="","",B12/B$5*100)</f>
-        <v/>
+        <v>76.1733072598387</v>
       </c>
       <c r="F12" s="6">
         <f>IF(C12="","",C12/C$5*100)</f>
-        <v/>
+        <v>89.2020497803807</v>
       </c>
       <c r="G12" s="6">
         <f>IF(D12="","",D12/D$5*100)</f>
-        <v/>
+        <v>67.9404841117628</v>
       </c>
       <c r="H12" s="6">
         <f>IF(OR(D12="",D11=""),"",(D12-D11)/D11*100)</f>
-        <v/>
+        <v>-2.35743375945433</v>
       </c>
       <c r="I12" s="6">
         <f>IF(OR(B12="",B11=""),"",(B12-B11)/B11*100)</f>
-        <v/>
+        <v>-6.99149380689449</v>
       </c>
       <c r="J12" s="6">
         <f>IF(OR(C12="",C11=""),"",(C12-C11)/C11*100)</f>
-        <v/>
+        <v>4.99784575613959</v>
       </c>
       <c r="L12" s="5">
         <f>'Raw data'!DZ3</f>
-        <v/>
+        <v>17424</v>
       </c>
       <c r="M12" s="5">
         <f>'Raw data'!EC3</f>
-        <v/>
+        <v>3793</v>
       </c>
       <c r="N12" s="5">
         <f>'Raw data'!EF3</f>
-        <v/>
+        <v>3713</v>
       </c>
       <c r="O12" s="5">
         <f>'Raw data'!EA3</f>
-        <v/>
+        <v>2396</v>
       </c>
       <c r="P12" s="5">
         <f>'Raw data'!ED3</f>
-        <v/>
+        <v>3332</v>
       </c>
       <c r="Q12" s="5">
         <f>'Raw data'!EG3</f>
-        <v/>
+        <v>1716</v>
       </c>
       <c r="R12" s="5">
         <f>'Raw data'!DW21</f>
-        <v/>
+        <v>2574</v>
       </c>
     </row>
     <row r="13">
@@ -28457,67 +29137,67 @@
       </c>
       <c r="B13" s="5">
         <f>'Raw data'!EN3</f>
-        <v/>
+        <v>27430</v>
       </c>
       <c r="C13" s="5">
         <f>'Raw data'!EO3</f>
-        <v/>
+        <v>2652</v>
       </c>
       <c r="D13" s="5">
         <f>'Raw data'!EP3</f>
-        <v/>
+        <v>727438</v>
       </c>
       <c r="E13" s="6">
         <f>IF(B13="","",B13/B$5*100)</f>
-        <v/>
+        <v>83.8120263994133</v>
       </c>
       <c r="F13" s="6">
         <f>IF(C13="","",C13/C$5*100)</f>
-        <v/>
+        <v>97.0717423133236</v>
       </c>
       <c r="G13" s="6">
         <f>IF(D13="","",D13/D$5*100)</f>
-        <v/>
+        <v>81.3493399238438</v>
       </c>
       <c r="H13" s="6">
         <f>IF(OR(D13="",D12=""),"",(D13-D12)/D12*100)</f>
-        <v/>
+        <v>19.7361793743231</v>
       </c>
       <c r="I13" s="6">
         <f>IF(OR(B13="",B12=""),"",(B13-B12)/B12*100)</f>
-        <v/>
+        <v>10.0280786201364</v>
       </c>
       <c r="J13" s="6">
         <f>IF(OR(C13="",C12=""),"",(C13-C12)/C12*100)</f>
-        <v/>
+        <v>8.82232252769799</v>
       </c>
       <c r="L13" s="5">
         <f>'Raw data'!EQ3</f>
-        <v/>
+        <v>20977</v>
       </c>
       <c r="M13" s="5">
         <f>'Raw data'!ET3</f>
-        <v/>
+        <v>3751</v>
       </c>
       <c r="N13" s="5">
         <f>'Raw data'!EW3</f>
-        <v/>
+        <v>2702</v>
       </c>
       <c r="O13" s="5">
         <f>'Raw data'!ER3</f>
-        <v/>
+        <v>2722</v>
       </c>
       <c r="P13" s="5">
         <f>'Raw data'!EU3</f>
-        <v/>
+        <v>2963</v>
       </c>
       <c r="Q13" s="5">
         <f>'Raw data'!EX3</f>
-        <v/>
+        <v>1676</v>
       </c>
       <c r="R13" s="5">
         <f>'Raw data'!EN21</f>
-        <v/>
+        <v>1797</v>
       </c>
     </row>
     <row r="14">
@@ -28526,67 +29206,67 @@
       </c>
       <c r="B14" s="5">
         <f>'Raw data'!FE3</f>
-        <v/>
+        <v>21472</v>
       </c>
       <c r="C14" s="5">
         <f>'Raw data'!FF3</f>
-        <v/>
+        <v>2750</v>
       </c>
       <c r="D14" s="5">
         <f>'Raw data'!FG3</f>
-        <v/>
+        <v>590532</v>
       </c>
       <c r="E14" s="6">
         <f>IF(B14="","",B14/B$5*100)</f>
-        <v/>
+        <v>65.607430945979</v>
       </c>
       <c r="F14" s="6">
         <f>IF(C14="","",C14/C$5*100)</f>
-        <v/>
+        <v>100.658857979502</v>
       </c>
       <c r="G14" s="6">
         <f>IF(D14="","",D14/D$5*100)</f>
-        <v/>
+        <v>66.0391516581583</v>
       </c>
       <c r="H14" s="6">
         <f>IF(OR(D14="",D13=""),"",(D14-D13)/D13*100)</f>
-        <v/>
+        <v>-18.8202980872597</v>
       </c>
       <c r="I14" s="6">
         <f>IF(OR(B14="",B13=""),"",(B14-B13)/B13*100)</f>
-        <v/>
+        <v>-21.720743711265</v>
       </c>
       <c r="J14" s="6">
         <f>IF(OR(C14="",C13=""),"",(C14-C13)/C13*100)</f>
-        <v/>
+        <v>3.69532428355958</v>
       </c>
       <c r="L14" s="5">
         <f>'Raw data'!FH3</f>
-        <v/>
+        <v>15596</v>
       </c>
       <c r="M14" s="5">
         <f>'Raw data'!FK3</f>
-        <v/>
+        <v>2975</v>
       </c>
       <c r="N14" s="5">
         <f>'Raw data'!FN3</f>
-        <v/>
+        <v>2901</v>
       </c>
       <c r="O14" s="5">
         <f>'Raw data'!FI3</f>
-        <v/>
+        <v>2772</v>
       </c>
       <c r="P14" s="5">
         <f>'Raw data'!FL3</f>
-        <v/>
+        <v>3647</v>
       </c>
       <c r="Q14" s="5">
         <f>'Raw data'!FO3</f>
-        <v/>
+        <v>1713</v>
       </c>
       <c r="R14" s="5">
         <f>'Raw data'!FE21</f>
-        <v/>
+        <v>1382</v>
       </c>
     </row>
     <row r="15">
@@ -28595,67 +29275,67 @@
       </c>
       <c r="B15" s="5">
         <f>'Raw data'!FV3</f>
-        <v/>
+        <v>20234</v>
       </c>
       <c r="C15" s="5">
         <f>'Raw data'!FW3</f>
-        <v/>
+        <v>2658</v>
       </c>
       <c r="D15" s="5">
         <f>'Raw data'!FX3</f>
-        <v/>
+        <v>537738</v>
       </c>
       <c r="E15" s="6">
         <f>IF(B15="","",B15/B$5*100)</f>
-        <v/>
+        <v>61.8247372280616</v>
       </c>
       <c r="F15" s="6">
         <f>IF(C15="","",C15/C$5*100)</f>
-        <v/>
+        <v>97.2913616398243</v>
       </c>
       <c r="G15" s="6">
         <f>IF(D15="","",D15/D$5*100)</f>
-        <v/>
+        <v>60.1352023842141</v>
       </c>
       <c r="H15" s="6">
         <f>IF(OR(D15="",D14=""),"",(D15-D14)/D14*100)</f>
-        <v/>
+        <v>-8.94007437361566</v>
       </c>
       <c r="I15" s="6">
         <f>IF(OR(B15="",B14=""),"",(B15-B14)/B14*100)</f>
-        <v/>
+        <v>-5.76564828614009</v>
       </c>
       <c r="J15" s="6">
         <f>IF(OR(C15="",C14=""),"",(C15-C14)/C14*100)</f>
-        <v/>
+        <v>-3.34545454545455</v>
       </c>
       <c r="L15" s="5">
         <f>'Raw data'!FY3</f>
-        <v/>
+        <v>14545</v>
       </c>
       <c r="M15" s="5">
         <f>'Raw data'!GB3</f>
-        <v/>
+        <v>3403</v>
       </c>
       <c r="N15" s="5">
         <f>'Raw data'!GE3</f>
-        <v/>
+        <v>2286</v>
       </c>
       <c r="O15" s="5">
         <f>'Raw data'!FZ3</f>
-        <v/>
+        <v>2526</v>
       </c>
       <c r="P15" s="5">
         <f>'Raw data'!GC3</f>
-        <v/>
+        <v>3875</v>
       </c>
       <c r="Q15" s="5">
         <f>'Raw data'!GF3</f>
-        <v/>
+        <v>1685</v>
       </c>
       <c r="R15" s="5">
         <f>'Raw data'!FV21</f>
-        <v/>
+        <v>1129</v>
       </c>
     </row>
     <row r="16">
@@ -28664,67 +29344,67 @@
       </c>
       <c r="B16" s="5">
         <f>'Raw data'!GM3</f>
-        <v/>
+        <v>22000</v>
       </c>
       <c r="C16" s="5">
         <f>'Raw data'!GN3</f>
-        <v/>
+        <v>2526</v>
       </c>
       <c r="D16" s="5">
         <f>'Raw data'!GO3</f>
-        <v/>
+        <v>555670</v>
       </c>
       <c r="E16" s="6">
         <f>IF(B16="","",B16/B$5*100)</f>
-        <v/>
+        <v>67.2207284282572</v>
       </c>
       <c r="F16" s="6">
         <f>IF(C16="","",C16/C$5*100)</f>
-        <v/>
+        <v>92.4597364568082</v>
       </c>
       <c r="G16" s="6">
         <f>IF(D16="","",D16/D$5*100)</f>
-        <v/>
+        <v>62.1405366718295</v>
       </c>
       <c r="H16" s="6">
         <f>IF(OR(D16="",D15=""),"",(D16-D15)/D15*100)</f>
-        <v/>
+        <v>3.33470946817967</v>
       </c>
       <c r="I16" s="6">
         <f>IF(OR(B16="",B15=""),"",(B16-B15)/B15*100)</f>
-        <v/>
+        <v>8.72788376000791</v>
       </c>
       <c r="J16" s="6">
         <f>IF(OR(C16="",C15=""),"",(C16-C15)/C15*100)</f>
-        <v/>
+        <v>-4.96613995485327</v>
       </c>
       <c r="L16" s="5">
         <f>'Raw data'!GP3</f>
-        <v/>
+        <v>15259</v>
       </c>
       <c r="M16" s="5">
         <f>'Raw data'!GS3</f>
-        <v/>
+        <v>3579</v>
       </c>
       <c r="N16" s="5">
         <f>'Raw data'!GV3</f>
-        <v/>
+        <v>3162</v>
       </c>
       <c r="O16" s="5">
         <f>'Raw data'!GQ3</f>
-        <v/>
+        <v>2580</v>
       </c>
       <c r="P16" s="5">
         <f>'Raw data'!GT3</f>
-        <v/>
+        <v>3407</v>
       </c>
       <c r="Q16" s="5">
         <f>'Raw data'!GW3</f>
-        <v/>
+        <v>1267</v>
       </c>
       <c r="R16" s="5">
         <f>'Raw data'!GM21</f>
-        <v/>
+        <v>1781</v>
       </c>
     </row>
     <row r="17">
@@ -28733,67 +29413,67 @@
       </c>
       <c r="B17" s="5">
         <f>'Raw data'!HD3</f>
-        <v/>
+        <v>20974</v>
       </c>
       <c r="C17" s="5">
         <f>'Raw data'!HE3</f>
-        <v/>
+        <v>2225</v>
       </c>
       <c r="D17" s="5">
         <f>'Raw data'!HF3</f>
-        <v/>
+        <v>466755</v>
       </c>
       <c r="E17" s="6">
         <f>IF(B17="","",B17/B$5*100)</f>
-        <v/>
+        <v>64.0857980933757</v>
       </c>
       <c r="F17" s="6">
         <f>IF(C17="","",C17/C$5*100)</f>
-        <v/>
+        <v>81.4421669106881</v>
       </c>
       <c r="G17" s="6">
         <f>IF(D17="","",D17/D$5*100)</f>
-        <v/>
+        <v>52.1971785308902</v>
       </c>
       <c r="H17" s="6">
         <f>IF(OR(D17="",D16=""),"",(D17-D16)/D16*100)</f>
-        <v/>
+        <v>-16.0014037108356</v>
       </c>
       <c r="I17" s="6">
         <f>IF(OR(B17="",B16=""),"",(B17-B16)/B16*100)</f>
-        <v/>
+        <v>-4.66363636363636</v>
       </c>
       <c r="J17" s="6">
         <f>IF(OR(C17="",C16=""),"",(C17-C16)/C16*100)</f>
-        <v/>
+        <v>-11.9160728424386</v>
       </c>
       <c r="L17" s="5">
         <f>'Raw data'!HG3</f>
-        <v/>
+        <v>14943</v>
       </c>
       <c r="M17" s="5">
         <f>'Raw data'!HJ3</f>
-        <v/>
+        <v>3244</v>
       </c>
       <c r="N17" s="5">
         <f>'Raw data'!HM3</f>
-        <v/>
+        <v>2787</v>
       </c>
       <c r="O17" s="5">
         <f>'Raw data'!HH3</f>
-        <v/>
+        <v>2152</v>
       </c>
       <c r="P17" s="5">
         <f>'Raw data'!HK3</f>
-        <v/>
+        <v>3048</v>
       </c>
       <c r="Q17" s="5">
         <f>'Raw data'!HN3</f>
-        <v/>
+        <v>1663</v>
       </c>
       <c r="R17" s="5">
         <f>'Raw data'!HD21</f>
-        <v/>
+        <v>1571</v>
       </c>
     </row>
     <row r="18">
@@ -28802,67 +29482,67 @@
       </c>
       <c r="B18" s="5">
         <f>'Raw data'!HU3</f>
-        <v/>
+        <v>23402</v>
       </c>
       <c r="C18" s="5">
         <f>'Raw data'!HV3</f>
-        <v/>
+        <v>2342</v>
       </c>
       <c r="D18" s="5">
         <f>'Raw data'!HW3</f>
-        <v/>
+        <v>548065</v>
       </c>
       <c r="E18" s="6">
         <f>IF(B18="","",B18/B$5*100)</f>
-        <v/>
+        <v>71.5045221217306</v>
       </c>
       <c r="F18" s="6">
         <f>IF(C18="","",C18/C$5*100)</f>
-        <v/>
+        <v>85.7247437774524</v>
       </c>
       <c r="G18" s="6">
         <f>IF(D18="","",D18/D$5*100)</f>
-        <v/>
+        <v>61.2900700614505</v>
       </c>
       <c r="H18" s="6">
         <f>IF(OR(D18="",D17=""),"",(D18-D17)/D17*100)</f>
-        <v/>
+        <v>17.4202740195606</v>
       </c>
       <c r="I18" s="6">
         <f>IF(OR(B18="",B17=""),"",(B18-B17)/B17*100)</f>
-        <v/>
+        <v>11.5762372461142</v>
       </c>
       <c r="J18" s="6">
         <f>IF(OR(C18="",C17=""),"",(C18-C17)/C17*100)</f>
-        <v/>
+        <v>5.25842696629213</v>
       </c>
       <c r="L18" s="5">
         <f>'Raw data'!HX3</f>
-        <v/>
+        <v>15819</v>
       </c>
       <c r="M18" s="5">
         <f>'Raw data'!IA3</f>
-        <v/>
+        <v>3462</v>
       </c>
       <c r="N18" s="5">
         <f>'Raw data'!ID3</f>
-        <v/>
+        <v>4121</v>
       </c>
       <c r="O18" s="5">
         <f>'Raw data'!HY3</f>
-        <v/>
+        <v>2435</v>
       </c>
       <c r="P18" s="5">
         <f>'Raw data'!IB3</f>
-        <v/>
+        <v>2652</v>
       </c>
       <c r="Q18" s="5">
         <f>'Raw data'!IE3</f>
-        <v/>
+        <v>1723</v>
       </c>
       <c r="R18" s="5">
         <f>'Raw data'!HU21</f>
-        <v/>
+        <v>2104</v>
       </c>
     </row>
     <row r="19">
@@ -28871,67 +29551,67 @@
       </c>
       <c r="B19" s="5">
         <f>'Raw data'!IL3</f>
-        <v/>
+        <v>26829</v>
       </c>
       <c r="C19" s="5">
         <f>'Raw data'!IM3</f>
-        <v/>
+        <v>2573</v>
       </c>
       <c r="D19" s="5">
         <f>'Raw data'!IN3</f>
-        <v/>
+        <v>690419</v>
       </c>
       <c r="E19" s="6">
         <f>IF(B19="","",B19/B$5*100)</f>
-        <v/>
+        <v>81.9756783182596</v>
       </c>
       <c r="F19" s="6">
         <f>IF(C19="","",C19/C$5*100)</f>
-        <v/>
+        <v>94.1800878477306</v>
       </c>
       <c r="G19" s="6">
         <f>IF(D19="","",D19/D$5*100)</f>
-        <v/>
+        <v>77.2095077805673</v>
       </c>
       <c r="H19" s="6">
         <f>IF(OR(D19="",D18=""),"",(D19-D18)/D18*100)</f>
-        <v/>
+        <v>25.9739264503298</v>
       </c>
       <c r="I19" s="6">
         <f>IF(OR(B19="",B18=""),"",(B19-B18)/B18*100)</f>
-        <v/>
+        <v>14.6440475173062</v>
       </c>
       <c r="J19" s="6">
         <f>IF(OR(C19="",C18=""),"",(C19-C18)/C18*100)</f>
-        <v/>
+        <v>9.86336464560205</v>
       </c>
       <c r="L19" s="5">
         <f>'Raw data'!IO3</f>
-        <v/>
+        <v>18150</v>
       </c>
       <c r="M19" s="5">
         <f>'Raw data'!IR3</f>
-        <v/>
+        <v>3844</v>
       </c>
       <c r="N19" s="5">
         <f>'Raw data'!IU3</f>
-        <v/>
+        <v>4835</v>
       </c>
       <c r="O19" s="5">
         <f>'Raw data'!IP3</f>
-        <v/>
+        <v>2567</v>
       </c>
       <c r="P19" s="5">
         <f>'Raw data'!IS3</f>
-        <v/>
+        <v>3634</v>
       </c>
       <c r="Q19" s="5">
         <f>'Raw data'!IV3</f>
-        <v/>
+        <v>1754</v>
       </c>
       <c r="R19" s="5">
         <f>'Raw data'!IL21</f>
-        <v/>
+        <v>1653</v>
       </c>
     </row>
     <row r="20">
@@ -28940,67 +29620,67 @@
       </c>
       <c r="B20" s="5">
         <f>'Raw data'!JC3</f>
-        <v/>
+        <v>23599</v>
       </c>
       <c r="C20" s="5">
         <f>'Raw data'!JD3</f>
-        <v/>
+        <v>2344</v>
       </c>
       <c r="D20" s="5">
         <f>'Raw data'!JE3</f>
-        <v/>
+        <v>553194</v>
       </c>
       <c r="E20" s="6">
         <f>IF(B20="","",B20/B$5*100)</f>
-        <v/>
+        <v>72.1064531899291</v>
       </c>
       <c r="F20" s="6">
         <f>IF(C20="","",C20/C$5*100)</f>
-        <v/>
+        <v>85.7979502196193</v>
       </c>
       <c r="G20" s="6">
         <f>IF(D20="","",D20/D$5*100)</f>
-        <v/>
+        <v>61.8636457675168</v>
       </c>
       <c r="H20" s="6">
         <f>IF(OR(D20="",D19=""),"",(D20-D19)/D19*100)</f>
-        <v/>
+        <v>-19.8756117661884</v>
       </c>
       <c r="I20" s="6">
         <f>IF(OR(B20="",B19=""),"",(B20-B19)/B19*100)</f>
-        <v/>
+        <v>-12.0392113012039</v>
       </c>
       <c r="J20" s="6">
         <f>IF(OR(C20="",C19=""),"",(C20-C19)/C19*100)</f>
-        <v/>
+        <v>-8.90011659541391</v>
       </c>
       <c r="L20" s="5">
         <f>'Raw data'!JF3</f>
-        <v/>
+        <v>16339</v>
       </c>
       <c r="M20" s="5">
         <f>'Raw data'!JI3</f>
-        <v/>
+        <v>3390</v>
       </c>
       <c r="N20" s="5">
         <f>'Raw data'!JL3</f>
-        <v/>
+        <v>3870</v>
       </c>
       <c r="O20" s="5">
         <f>'Raw data'!JG3</f>
-        <v/>
+        <v>2303</v>
       </c>
       <c r="P20" s="5">
         <f>'Raw data'!JJ3</f>
-        <v/>
+        <v>3524</v>
       </c>
       <c r="Q20" s="5">
         <f>'Raw data'!JM3</f>
-        <v/>
+        <v>1483</v>
       </c>
       <c r="R20" s="5">
         <f>'Raw data'!JC21</f>
-        <v/>
+        <v>1565</v>
       </c>
     </row>
     <row r="21">
@@ -29009,67 +29689,67 @@
       </c>
       <c r="B21" s="5">
         <f>'Raw data'!JT3</f>
-        <v/>
+        <v>21745</v>
       </c>
       <c r="C21" s="5">
         <f>'Raw data'!JU3</f>
-        <v/>
+        <v>2552</v>
       </c>
       <c r="D21" s="5">
         <f>'Raw data'!JV3</f>
-        <v/>
+        <v>554893</v>
       </c>
       <c r="E21" s="6">
         <f>IF(B21="","",B21/B$5*100)</f>
-        <v/>
+        <v>66.4415790760205</v>
       </c>
       <c r="F21" s="6">
         <f>IF(C21="","",C21/C$5*100)</f>
-        <v/>
+        <v>93.411420204978</v>
       </c>
       <c r="G21" s="6">
         <f>IF(D21="","",D21/D$5*100)</f>
-        <v/>
+        <v>62.0536448169624</v>
       </c>
       <c r="H21" s="6">
         <f>IF(OR(D21="",D20=""),"",(D21-D20)/D20*100)</f>
-        <v/>
+        <v>0.307125529199521</v>
       </c>
       <c r="I21" s="6">
         <f>IF(OR(B21="",B20=""),"",(B21-B20)/B20*100)</f>
-        <v/>
+        <v>-7.85626509597864</v>
       </c>
       <c r="J21" s="6">
         <f>IF(OR(C21="",C20=""),"",(C21-C20)/C20*100)</f>
-        <v/>
+        <v>8.87372013651877</v>
       </c>
       <c r="L21" s="5">
         <f>'Raw data'!JW3</f>
-        <v/>
+        <v>14266</v>
       </c>
       <c r="M21" s="5">
         <f>'Raw data'!JZ3</f>
-        <v/>
+        <v>3888</v>
       </c>
       <c r="N21" s="5">
         <f>'Raw data'!KC3</f>
-        <v/>
+        <v>3591</v>
       </c>
       <c r="O21" s="5">
         <f>'Raw data'!JX3</f>
-        <v/>
+        <v>2661</v>
       </c>
       <c r="P21" s="5">
         <f>'Raw data'!KA3</f>
-        <v/>
+        <v>3037</v>
       </c>
       <c r="Q21" s="5">
         <f>'Raw data'!KD3</f>
-        <v/>
+        <v>1591</v>
       </c>
       <c r="R21" s="5">
         <f>'Raw data'!JT21</f>
-        <v/>
+        <v>1732</v>
       </c>
     </row>
     <row r="22">
@@ -29078,67 +29758,67 @@
       </c>
       <c r="B22" s="5">
         <f>'Raw data'!KK3</f>
-        <v/>
+        <v>20088</v>
       </c>
       <c r="C22" s="5">
         <f>'Raw data'!KL3</f>
-        <v/>
+        <v>2392</v>
       </c>
       <c r="D22" s="5">
         <f>'Raw data'!KM3</f>
-        <v/>
+        <v>480601</v>
       </c>
       <c r="E22" s="6">
         <f>IF(B22="","",B22/B$5*100)</f>
-        <v/>
+        <v>61.3786360303104</v>
       </c>
       <c r="F22" s="6">
         <f>IF(C22="","",C22/C$5*100)</f>
-        <v/>
+        <v>87.5549048316252</v>
       </c>
       <c r="G22" s="6">
         <f>IF(D22="","",D22/D$5*100)</f>
-        <v/>
+        <v>53.7455757284322</v>
       </c>
       <c r="H22" s="6">
         <f>IF(OR(D22="",D21=""),"",(D22-D21)/D21*100)</f>
-        <v/>
+        <v>-13.388527157488</v>
       </c>
       <c r="I22" s="6">
         <f>IF(OR(B22="",B21=""),"",(B22-B21)/B21*100)</f>
-        <v/>
+        <v>-7.62014256150839</v>
       </c>
       <c r="J22" s="6">
         <f>IF(OR(C22="",C21=""),"",(C22-C21)/C21*100)</f>
-        <v/>
+        <v>-6.26959247648903</v>
       </c>
       <c r="L22" s="5">
         <f>'Raw data'!KN3</f>
-        <v/>
+        <v>13017</v>
       </c>
       <c r="M22" s="5">
         <f>'Raw data'!KQ3</f>
-        <v/>
+        <v>3495</v>
       </c>
       <c r="N22" s="5">
         <f>'Raw data'!KT3</f>
-        <v/>
+        <v>3576</v>
       </c>
       <c r="O22" s="5">
         <f>'Raw data'!KO3</f>
-        <v/>
+        <v>2329</v>
       </c>
       <c r="P22" s="5">
         <f>'Raw data'!KR3</f>
-        <v/>
+        <v>3562</v>
       </c>
       <c r="Q22" s="5">
         <f>'Raw data'!KU3</f>
-        <v/>
+        <v>1479</v>
       </c>
       <c r="R22" s="5">
         <f>'Raw data'!KK21</f>
-        <v/>
+        <v>1759</v>
       </c>
     </row>
     <row r="23">
@@ -29147,67 +29827,67 @@
       </c>
       <c r="B23" s="5">
         <f>'Raw data'!LB3</f>
-        <v/>
+        <v>22525</v>
       </c>
       <c r="C23" s="5">
         <f>'Raw data'!LC3</f>
-        <v/>
+        <v>2443</v>
       </c>
       <c r="D23" s="5">
         <f>'Raw data'!LD3</f>
-        <v/>
+        <v>550293</v>
       </c>
       <c r="E23" s="6">
         <f>IF(B23="","",B23/B$5*100)</f>
-        <v/>
+        <v>68.8248594475678</v>
       </c>
       <c r="F23" s="6">
         <f>IF(C23="","",C23/C$5*100)</f>
-        <v/>
+        <v>89.4216691068814</v>
       </c>
       <c r="G23" s="6">
         <f>IF(D23="","",D23/D$5*100)</f>
-        <v/>
+        <v>61.5392271433604</v>
       </c>
       <c r="H23" s="6">
         <f>IF(OR(D23="",D22=""),"",(D23-D22)/D22*100)</f>
-        <v/>
+        <v>14.5010101934869</v>
       </c>
       <c r="I23" s="6">
         <f>IF(OR(B23="",B22=""),"",(B23-B22)/B22*100)</f>
-        <v/>
+        <v>12.13162086818</v>
       </c>
       <c r="J23" s="6">
         <f>IF(OR(C23="",C22=""),"",(C23-C22)/C22*100)</f>
-        <v/>
+        <v>2.13210702341137</v>
       </c>
       <c r="L23" s="5">
         <f>'Raw data'!LE3</f>
-        <v/>
+        <v>14699</v>
       </c>
       <c r="M23" s="5">
         <f>'Raw data'!LH3</f>
-        <v/>
+        <v>3835</v>
       </c>
       <c r="N23" s="5">
         <f>'Raw data'!LK3</f>
-        <v/>
+        <v>3992</v>
       </c>
       <c r="O23" s="5">
         <f>'Raw data'!LF3</f>
-        <v/>
+        <v>2436</v>
       </c>
       <c r="P23" s="5">
         <f>'Raw data'!LI3</f>
-        <v/>
+        <v>3304</v>
       </c>
       <c r="Q23" s="5">
         <f>'Raw data'!LL3</f>
-        <v/>
+        <v>1643</v>
       </c>
       <c r="R23" s="5">
         <f>'Raw data'!LB21</f>
-        <v/>
+        <v>1238</v>
       </c>
     </row>
     <row r="24">
@@ -29216,67 +29896,92 @@
       </c>
       <c r="B24" s="5">
         <f>'Raw data'!LS3</f>
-        <v/>
+        <v>23969</v>
       </c>
       <c r="C24" s="5">
         <f>'Raw data'!LT3</f>
-        <v/>
+        <v>2474</v>
       </c>
       <c r="D24" s="5">
         <f>'Raw data'!LU3</f>
-        <v/>
+        <v>593017</v>
       </c>
       <c r="E24" s="6">
         <f>IF(B24="","",B24/B$5*100)</f>
-        <v/>
+        <v>73.2369836225862</v>
       </c>
       <c r="F24" s="6">
         <f>IF(C24="","",C24/C$5*100)</f>
-        <v/>
+        <v>90.5563689604685</v>
       </c>
       <c r="G24" s="6">
         <f>IF(D24="","",D24/D$5*100)</f>
-        <v/>
+        <v>66.3170490318324</v>
       </c>
       <c r="H24" s="6">
         <f>IF(OR(D24="",D23=""),"",(D24-D23)/D23*100)</f>
-        <v/>
+        <v>7.76386397791722</v>
       </c>
       <c r="I24" s="6">
         <f>IF(OR(B24="",B23=""),"",(B24-B23)/B23*100)</f>
-        <v/>
+        <v>6.41065482796892</v>
       </c>
       <c r="J24" s="6">
         <f>IF(OR(C24="",C23=""),"",(C24-C23)/C23*100)</f>
-        <v/>
+        <v>1.26893164142448</v>
       </c>
       <c r="L24" s="5">
         <f>'Raw data'!LV3</f>
-        <v/>
+        <v>15521</v>
       </c>
       <c r="M24" s="5">
         <f>'Raw data'!LY3</f>
-        <v/>
+        <v>3928</v>
       </c>
       <c r="N24" s="5">
         <f>'Raw data'!MB3</f>
-        <v/>
+        <v>4520</v>
       </c>
       <c r="O24" s="5">
         <f>'Raw data'!LW3</f>
-        <v/>
+        <v>2562</v>
       </c>
       <c r="P24" s="5">
         <f>'Raw data'!LZ3</f>
-        <v/>
+        <v>3218</v>
       </c>
       <c r="Q24" s="5">
         <f>'Raw data'!MC3</f>
-        <v/>
+        <v>1527</v>
       </c>
       <c r="R24" s="5">
         <f>'Raw data'!LS21</f>
-        <v/>
+        <v>1803</v>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>시작연도 대비
+전체 변화율(%)</t>
+        </is>
+      </c>
+      <c r="B26" s="7">
+        <f>(INDEX(B5:B24,COUNT(B5:B24))-B5)/B5*100</f>
+        <v>-26.7630163774138</v>
+      </c>
+      <c r="C26" s="7">
+        <f>(INDEX(C5:C24,COUNT(C5:C24))-C5)/C5*100</f>
+        <v>-9.44363103953148</v>
+      </c>
+      <c r="D26" s="7">
+        <f>(INDEX(D5:D24,COUNT(D5:D24))-D5)/D5*100</f>
+        <v>-33.6829509681676</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>← (최종연도 값 − 시작연도 값) ÷ 시작연도 값 × 100 (최종연도 = 자료가 있는 마지막 연도)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -29290,53 +29995,55 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>표 1. 시작연도(2005년) 대비 전체 변화율</t>
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>표 1. 요약표: 시작연도·5년 간격 연도·최종연도 (전국 감자)</t>
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="32" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>시작연도</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>시작연도 값</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>최종연도</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>최종연도 값</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>전체 변화율(%)</t>
+      <c r="B3" s="9">
+        <f>분석!A5</f>
+        <v>2005</v>
+      </c>
+      <c r="C3" s="9">
+        <f>B3+5</f>
+        <v>2010</v>
+      </c>
+      <c r="D3" s="9">
+        <f>C3+5</f>
+        <v>2015</v>
+      </c>
+      <c r="E3" s="9">
+        <f>D3+5</f>
+        <v>2020</v>
+      </c>
+      <c r="F3" s="9">
+        <f>INDEX(분석!A5:A24,COUNT(분석!D5:D24))</f>
+        <v>2024</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>전체 변화율(%)
+(시작→최종)</t>
         </is>
       </c>
     </row>
@@ -29346,25 +30053,29 @@
           <t>재배면적(ha)</t>
         </is>
       </c>
-      <c r="B4" s="4">
-        <f>분석!A5</f>
-        <v/>
+      <c r="B4" s="5">
+        <f>INDEX(분석!$B$5:$B$24,MATCH(B$3,분석!$A$5:$A$24,0))</f>
+        <v>32728</v>
       </c>
       <c r="C4" s="5">
-        <f>분석!B5</f>
-        <v/>
-      </c>
-      <c r="D4" s="4">
-        <f>INDEX(분석!A5:A24,COUNT(분석!B5:B24))</f>
-        <v/>
+        <f>INDEX(분석!$B$5:$B$24,MATCH(C$3,분석!$A$5:$A$24,0))</f>
+        <v>24913</v>
+      </c>
+      <c r="D4" s="5">
+        <f>INDEX(분석!$B$5:$B$24,MATCH(D$3,분석!$A$5:$A$24,0))</f>
+        <v>20234</v>
       </c>
       <c r="E4" s="5">
-        <f>INDEX(분석!B5:B24,COUNT(분석!B5:B24))</f>
-        <v/>
-      </c>
-      <c r="F4" s="6">
-        <f>(E4-C4)/C4*100</f>
-        <v/>
+        <f>INDEX(분석!$B$5:$B$24,MATCH(E$3,분석!$A$5:$A$24,0))</f>
+        <v>23599</v>
+      </c>
+      <c r="F4" s="5">
+        <f>INDEX(분석!$B$5:$B$24,MATCH(F$3,분석!$A$5:$A$24,0))</f>
+        <v>23969</v>
+      </c>
+      <c r="G4" s="6">
+        <f>분석!B26</f>
+        <v>-26.7630163774138</v>
       </c>
     </row>
     <row r="5">
@@ -29373,25 +30084,29 @@
           <t>단수(kg/10a)</t>
         </is>
       </c>
-      <c r="B5" s="4">
-        <f>분석!A5</f>
-        <v/>
+      <c r="B5" s="5">
+        <f>INDEX(분석!$C$5:$C$24,MATCH(B$3,분석!$A$5:$A$24,0))</f>
+        <v>2732</v>
       </c>
       <c r="C5" s="5">
-        <f>분석!C5</f>
-        <v/>
-      </c>
-      <c r="D5" s="4">
-        <f>INDEX(분석!A5:A24,COUNT(분석!C5:C24))</f>
-        <v/>
+        <f>INDEX(분석!$C$5:$C$24,MATCH(C$3,분석!$A$5:$A$24,0))</f>
+        <v>2475</v>
+      </c>
+      <c r="D5" s="5">
+        <f>INDEX(분석!$C$5:$C$24,MATCH(D$3,분석!$A$5:$A$24,0))</f>
+        <v>2658</v>
       </c>
       <c r="E5" s="5">
-        <f>INDEX(분석!C5:C24,COUNT(분석!C5:C24))</f>
-        <v/>
-      </c>
-      <c r="F5" s="6">
-        <f>(E5-C5)/C5*100</f>
-        <v/>
+        <f>INDEX(분석!$C$5:$C$24,MATCH(E$3,분석!$A$5:$A$24,0))</f>
+        <v>2344</v>
+      </c>
+      <c r="F5" s="5">
+        <f>INDEX(분석!$C$5:$C$24,MATCH(F$3,분석!$A$5:$A$24,0))</f>
+        <v>2474</v>
+      </c>
+      <c r="G5" s="6">
+        <f>분석!C26</f>
+        <v>-9.44363103953148</v>
       </c>
     </row>
     <row r="6">
@@ -29400,116 +30115,223 @@
           <t>총생산량(톤)</t>
         </is>
       </c>
-      <c r="B6" s="4">
-        <f>분석!A5</f>
-        <v/>
+      <c r="B6" s="5">
+        <f>INDEX(분석!$D$5:$D$24,MATCH(B$3,분석!$A$5:$A$24,0))</f>
+        <v>894215</v>
       </c>
       <c r="C6" s="5">
-        <f>분석!D5</f>
-        <v/>
-      </c>
-      <c r="D6" s="4">
-        <f>INDEX(분석!A5:A24,COUNT(분석!D5:D24))</f>
-        <v/>
+        <f>INDEX(분석!$D$5:$D$24,MATCH(C$3,분석!$A$5:$A$24,0))</f>
+        <v>616707</v>
+      </c>
+      <c r="D6" s="5">
+        <f>INDEX(분석!$D$5:$D$24,MATCH(D$3,분석!$A$5:$A$24,0))</f>
+        <v>537738</v>
       </c>
       <c r="E6" s="5">
-        <f>INDEX(분석!D5:D24,COUNT(분석!D5:D24))</f>
-        <v/>
-      </c>
-      <c r="F6" s="6">
-        <f>(E6-C6)/C6*100</f>
-        <v/>
+        <f>INDEX(분석!$D$5:$D$24,MATCH(E$3,분석!$A$5:$A$24,0))</f>
+        <v>553194</v>
+      </c>
+      <c r="F6" s="5">
+        <f>INDEX(분석!$D$5:$D$24,MATCH(F$3,분석!$A$5:$A$24,0))</f>
+        <v>593017</v>
+      </c>
+      <c r="G6" s="6">
+        <f>분석!D26</f>
+        <v>-33.6829509681676</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>※ 전체 변화율(%) = (최종연도 값 − 시작연도 값) ÷ 시작연도 값 × 100</t>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>재배면적 지수(2005=100)</t>
+        </is>
+      </c>
+      <c r="B7" s="6">
+        <f>INDEX(분석!$E$5:$E$24,MATCH(B$3,분석!$A$5:$A$24,0))</f>
+        <v>100</v>
+      </c>
+      <c r="C7" s="6">
+        <f>INDEX(분석!$E$5:$E$24,MATCH(C$3,분석!$A$5:$A$24,0))</f>
+        <v>76.1213639696896</v>
+      </c>
+      <c r="D7" s="6">
+        <f>INDEX(분석!$E$5:$E$24,MATCH(D$3,분석!$A$5:$A$24,0))</f>
+        <v>61.8247372280616</v>
+      </c>
+      <c r="E7" s="6">
+        <f>INDEX(분석!$E$5:$E$24,MATCH(E$3,분석!$A$5:$A$24,0))</f>
+        <v>72.1064531899291</v>
+      </c>
+      <c r="F7" s="6">
+        <f>INDEX(분석!$E$5:$E$24,MATCH(F$3,분석!$A$5:$A$24,0))</f>
+        <v>73.2369836225862</v>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>단수 지수(2005=100)</t>
+        </is>
+      </c>
+      <c r="B8" s="6">
+        <f>INDEX(분석!$F$5:$F$24,MATCH(B$3,분석!$A$5:$A$24,0))</f>
+        <v>100</v>
+      </c>
+      <c r="C8" s="6">
+        <f>INDEX(분석!$F$5:$F$24,MATCH(C$3,분석!$A$5:$A$24,0))</f>
+        <v>90.592972181552</v>
+      </c>
+      <c r="D8" s="6">
+        <f>INDEX(분석!$F$5:$F$24,MATCH(D$3,분석!$A$5:$A$24,0))</f>
+        <v>97.2913616398243</v>
+      </c>
+      <c r="E8" s="6">
+        <f>INDEX(분석!$F$5:$F$24,MATCH(E$3,분석!$A$5:$A$24,0))</f>
+        <v>85.7979502196193</v>
+      </c>
+      <c r="F8" s="6">
+        <f>INDEX(분석!$F$5:$F$24,MATCH(F$3,분석!$A$5:$A$24,0))</f>
+        <v>90.5563689604685</v>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>표 2. 전년 대비 변화가 두드러진 연도</t>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>생산량 지수(2005=100)</t>
+        </is>
+      </c>
+      <c r="B9" s="6">
+        <f>INDEX(분석!$G$5:$G$24,MATCH(B$3,분석!$A$5:$A$24,0))</f>
+        <v>100</v>
+      </c>
+      <c r="C9" s="6">
+        <f>INDEX(분석!$G$5:$G$24,MATCH(C$3,분석!$A$5:$A$24,0))</f>
+        <v>68.9663000508826</v>
+      </c>
+      <c r="D9" s="6">
+        <f>INDEX(분석!$G$5:$G$24,MATCH(D$3,분석!$A$5:$A$24,0))</f>
+        <v>60.1352023842141</v>
+      </c>
+      <c r="E9" s="6">
+        <f>INDEX(분석!$G$5:$G$24,MATCH(E$3,분석!$A$5:$A$24,0))</f>
+        <v>61.8636457675168</v>
+      </c>
+      <c r="F9" s="6">
+        <f>INDEX(분석!$G$5:$G$24,MATCH(F$3,분석!$A$5:$A$24,0))</f>
+        <v>66.3170490318324</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>연도</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>값</t>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>※ 전체 변화율(%) = (최종연도 값 − 시작연도 값) ÷ 시작연도 값 × 100,  지수 = 해당연도 값 ÷ 시작연도 값 × 100</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>생산량 최대 감소율(%)</t>
-        </is>
-      </c>
-      <c r="B11" s="4">
-        <f>INDEX(분석!A6:A24,MATCH(C11,분석!H6:H24,0))</f>
-        <v/>
-      </c>
-      <c r="C11" s="6">
-        <f>MIN(분석!H6:H24)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>생산량 최대 증가율(%)</t>
-        </is>
-      </c>
-      <c r="B12" s="4">
-        <f>INDEX(분석!A6:A24,MATCH(C12,분석!H6:H24,0))</f>
-        <v/>
-      </c>
-      <c r="C12" s="6">
-        <f>MAX(분석!H6:H24)</f>
-        <v/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>※ 자료: 국가데이터처 KOSIS 「농작물생산조사」 통계표 '서류생산량(생서)'(감자 합계, 전국), 다운로드일 2026.10.10</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>단수 최저값(kg/10a)</t>
-        </is>
-      </c>
-      <c r="B13" s="4">
-        <f>INDEX(분석!A5:A24,MATCH(C13,분석!C5:C24,0))</f>
-        <v/>
-      </c>
-      <c r="C13" s="5">
-        <f>MIN(분석!C5:C24)</f>
-        <v/>
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>표 2. 전년 대비 변화가 두드러진 연도</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>연도</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>생산량 최대 감소율(%)</t>
+        </is>
+      </c>
+      <c r="B15" s="4">
+        <f>INDEX(분석!A6:A24,MATCH(C15,분석!H6:H24,0))</f>
+        <v>2006</v>
+      </c>
+      <c r="C15" s="6">
+        <f>MIN(분석!H6:H24)</f>
+        <v>-29.425697399395</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>생산량 최대 증가율(%)</t>
+        </is>
+      </c>
+      <c r="B16" s="4">
+        <f>INDEX(분석!A6:A24,MATCH(C16,분석!H6:H24,0))</f>
+        <v>2019</v>
+      </c>
+      <c r="C16" s="6">
+        <f>MAX(분석!H6:H24)</f>
+        <v>25.9739264503298</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>단수 최저값(kg/10a)</t>
+        </is>
+      </c>
+      <c r="B17" s="4">
+        <f>INDEX(분석!A5:A24,MATCH(C17,분석!C5:C24,0))</f>
+        <v>2017</v>
+      </c>
+      <c r="C17" s="5">
+        <f>MIN(분석!C5:C24)</f>
+        <v>2225</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>재배면적 최대 감소율(%)</t>
         </is>
       </c>
-      <c r="B14" s="4">
-        <f>INDEX(분석!A6:A24,MATCH(C14,분석!I6:I24,0))</f>
-        <v/>
-      </c>
-      <c r="C14" s="6">
+      <c r="B18" s="4">
+        <f>INDEX(분석!A6:A24,MATCH(C18,분석!I6:I24,0))</f>
+        <v>2006</v>
+      </c>
+      <c r="C18" s="6">
         <f>MIN(분석!I6:I24)</f>
-        <v/>
+        <v>-26.7996822292838</v>
       </c>
     </row>
   </sheetData>

--- a/assignments/식용작물학1_감자_분석.xlsx
+++ b/assignments/식용작물학1_감자_분석.xlsx
@@ -60,7 +60,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -82,11 +82,55 @@
         <color rgb="00999999"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00999999"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="00999999"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00999999"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="00999999"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -108,6 +152,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -28432,10 +28482,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R26"/>
+  <dimension ref="A1:U41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -28453,6 +28503,9 @@
     <col width="15" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="20" max="20"/>
+    <col width="15" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -28575,6 +28628,24 @@
 감자 면적(ha)</t>
         </is>
       </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>[참고] 일반봄감자 면적
+전년 대비(%)</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>[참고] 고랭지감자 면적
+전년 대비(%)</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>[참고] 가을감자 면적
+전년 대비(%)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -28647,6 +28718,21 @@
         <f>'Raw data'!H21</f>
         <v>6174</v>
       </c>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -28716,6 +28802,18 @@
         <f>'Raw data'!Y21</f>
         <v>4167</v>
       </c>
+      <c r="S6" s="6">
+        <f>IF(OR(L6="",L5=""),"",(L6-L5)/L5*100)</f>
+        <v>-25.3306713251809</v>
+      </c>
+      <c r="T6" s="6">
+        <f>IF(OR(M6="",M5=""),"",(M6-M5)/M5*100)</f>
+        <v>-9.44127708095781</v>
+      </c>
+      <c r="U6" s="6">
+        <f>IF(OR(N6="",N5=""),"",(N6-N5)/N5*100)</f>
+        <v>-39.5040924410207</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -28785,6 +28883,18 @@
         <f>'Raw data'!AP21</f>
         <v>2717</v>
       </c>
+      <c r="S7" s="6">
+        <f>IF(OR(L7="",L6=""),"",(L7-L6)/L6*100)</f>
+        <v>-12.8810160427807</v>
+      </c>
+      <c r="T7" s="6">
+        <f>IF(OR(M7="",M6=""),"",(M7-M6)/M6*100)</f>
+        <v>-19.3653991437925</v>
+      </c>
+      <c r="U7" s="6">
+        <f>IF(OR(N7="",N6=""),"",(N7-N6)/N6*100)</f>
+        <v>-16.7130919220056</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -28854,6 +28964,18 @@
         <f>'Raw data'!BG21</f>
         <v>2663</v>
       </c>
+      <c r="S8" s="6">
+        <f>IF(OR(L8="",L7=""),"",(L8-L7)/L7*100)</f>
+        <v>0.115092457607611</v>
+      </c>
+      <c r="T8" s="6">
+        <f>IF(OR(M8="",M7=""),"",(M8-M7)/M7*100)</f>
+        <v>5.05933791380387</v>
+      </c>
+      <c r="U8" s="6">
+        <f>IF(OR(N8="",N7=""),"",(N8-N7)/N7*100)</f>
+        <v>-1.38557095078834</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -28923,6 +29045,18 @@
         <f>'Raw data'!BX21</f>
         <v>2413</v>
       </c>
+      <c r="S9" s="6">
+        <f>IF(OR(L9="",L8=""),"",(L9-L8)/L8*100)</f>
+        <v>8.81361128142244</v>
+      </c>
+      <c r="T9" s="6">
+        <f>IF(OR(M9="",M8=""),"",(M9-M8)/M8*100)</f>
+        <v>-1.24851367419738</v>
+      </c>
+      <c r="U9" s="6">
+        <f>IF(OR(N9="",N8=""),"",(N9-N8)/N8*100)</f>
+        <v>-6.1046511627907</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -28992,6 +29126,18 @@
         <f>'Raw data'!CO21</f>
         <v>2766</v>
       </c>
+      <c r="S10" s="6">
+        <f>IF(OR(L10="",L9=""),"",(L10-L9)/L9*100)</f>
+        <v>14.8189885899422</v>
+      </c>
+      <c r="T10" s="6">
+        <f>IF(OR(M10="",M9=""),"",(M10-M9)/M9*100)</f>
+        <v>14.4190246839253</v>
+      </c>
+      <c r="U10" s="6">
+        <f>IF(OR(N10="",N9=""),"",(N10-N9)/N9*100)</f>
+        <v>24.0970072239422</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -29061,6 +29207,18 @@
         <f>'Raw data'!DF21</f>
         <v>2814</v>
       </c>
+      <c r="S11" s="6">
+        <f>IF(OR(L11="",L10=""),"",(L11-L10)/L10*100)</f>
+        <v>17.3230278493436</v>
+      </c>
+      <c r="T11" s="6">
+        <f>IF(OR(M11="",M10=""),"",(M11-M10)/M10*100)</f>
+        <v>-0.447250723493817</v>
+      </c>
+      <c r="U11" s="6">
+        <f>IF(OR(N11="",N10=""),"",(N11-N10)/N10*100)</f>
+        <v>-19.043659043659</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -29130,6 +29288,18 @@
         <f>'Raw data'!DW21</f>
         <v>2574</v>
       </c>
+      <c r="S12" s="6">
+        <f>IF(OR(L12="",L11=""),"",(L12-L11)/L11*100)</f>
+        <v>-8.89888110425599</v>
+      </c>
+      <c r="T12" s="6">
+        <f>IF(OR(M12="",M11=""),"",(M12-M11)/M11*100)</f>
+        <v>0.23784355179704</v>
+      </c>
+      <c r="U12" s="6">
+        <f>IF(OR(N12="",N11=""),"",(N12-N11)/N11*100)</f>
+        <v>-4.64817668207499</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -29199,6 +29369,18 @@
         <f>'Raw data'!EN21</f>
         <v>1797</v>
       </c>
+      <c r="S13" s="6">
+        <f>IF(OR(L13="",L12=""),"",(L13-L12)/L12*100)</f>
+        <v>20.3914141414141</v>
+      </c>
+      <c r="T13" s="6">
+        <f>IF(OR(M13="",M12=""),"",(M13-M12)/M12*100)</f>
+        <v>-1.10730292644345</v>
+      </c>
+      <c r="U13" s="6">
+        <f>IF(OR(N13="",N12=""),"",(N13-N12)/N12*100)</f>
+        <v>-27.2286560732561</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -29268,6 +29450,18 @@
         <f>'Raw data'!FE21</f>
         <v>1382</v>
       </c>
+      <c r="S14" s="6">
+        <f>IF(OR(L14="",L13=""),"",(L14-L13)/L13*100)</f>
+        <v>-25.651904466797</v>
+      </c>
+      <c r="T14" s="6">
+        <f>IF(OR(M14="",M13=""),"",(M14-M13)/M13*100)</f>
+        <v>-20.6878165822447</v>
+      </c>
+      <c r="U14" s="6">
+        <f>IF(OR(N14="",N13=""),"",(N14-N13)/N13*100)</f>
+        <v>7.36491487786825</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -29337,6 +29531,18 @@
         <f>'Raw data'!FV21</f>
         <v>1129</v>
       </c>
+      <c r="S15" s="6">
+        <f>IF(OR(L15="",L14=""),"",(L15-L14)/L14*100)</f>
+        <v>-6.73890741215696</v>
+      </c>
+      <c r="T15" s="6">
+        <f>IF(OR(M15="",M14=""),"",(M15-M14)/M14*100)</f>
+        <v>14.3865546218487</v>
+      </c>
+      <c r="U15" s="6">
+        <f>IF(OR(N15="",N14=""),"",(N15-N14)/N14*100)</f>
+        <v>-21.1995863495346</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -29406,6 +29612,18 @@
         <f>'Raw data'!GM21</f>
         <v>1781</v>
       </c>
+      <c r="S16" s="6">
+        <f>IF(OR(L16="",L15=""),"",(L16-L15)/L15*100)</f>
+        <v>4.90890340323135</v>
+      </c>
+      <c r="T16" s="6">
+        <f>IF(OR(M16="",M15=""),"",(M16-M15)/M15*100)</f>
+        <v>5.17190714075815</v>
+      </c>
+      <c r="U16" s="6">
+        <f>IF(OR(N16="",N15=""),"",(N16-N15)/N15*100)</f>
+        <v>38.3202099737533</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -29475,6 +29693,18 @@
         <f>'Raw data'!HD21</f>
         <v>1571</v>
       </c>
+      <c r="S17" s="6">
+        <f>IF(OR(L17="",L16=""),"",(L17-L16)/L16*100)</f>
+        <v>-2.07090897175437</v>
+      </c>
+      <c r="T17" s="6">
+        <f>IF(OR(M17="",M16=""),"",(M17-M16)/M16*100)</f>
+        <v>-9.36015646828723</v>
+      </c>
+      <c r="U17" s="6">
+        <f>IF(OR(N17="",N16=""),"",(N17-N16)/N16*100)</f>
+        <v>-11.8595825426945</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -29544,6 +29774,18 @@
         <f>'Raw data'!HU21</f>
         <v>2104</v>
       </c>
+      <c r="S18" s="6">
+        <f>IF(OR(L18="",L17=""),"",(L18-L17)/L17*100)</f>
+        <v>5.86227665127484</v>
+      </c>
+      <c r="T18" s="6">
+        <f>IF(OR(M18="",M17=""),"",(M18-M17)/M17*100)</f>
+        <v>6.72009864364981</v>
+      </c>
+      <c r="U18" s="6">
+        <f>IF(OR(N18="",N17=""),"",(N18-N17)/N17*100)</f>
+        <v>47.865087908145</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -29613,6 +29855,18 @@
         <f>'Raw data'!IL21</f>
         <v>1653</v>
       </c>
+      <c r="S19" s="6">
+        <f>IF(OR(L19="",L18=""),"",(L19-L18)/L18*100)</f>
+        <v>14.7354447183766</v>
+      </c>
+      <c r="T19" s="6">
+        <f>IF(OR(M19="",M18=""),"",(M19-M18)/M18*100)</f>
+        <v>11.0340843443096</v>
+      </c>
+      <c r="U19" s="6">
+        <f>IF(OR(N19="",N18=""),"",(N19-N18)/N18*100)</f>
+        <v>17.3258917738413</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -29682,6 +29936,18 @@
         <f>'Raw data'!JC21</f>
         <v>1565</v>
       </c>
+      <c r="S20" s="6">
+        <f>IF(OR(L20="",L19=""),"",(L20-L19)/L19*100)</f>
+        <v>-9.97796143250689</v>
+      </c>
+      <c r="T20" s="6">
+        <f>IF(OR(M20="",M19=""),"",(M20-M19)/M19*100)</f>
+        <v>-11.8106139438085</v>
+      </c>
+      <c r="U20" s="6">
+        <f>IF(OR(N20="",N19=""),"",(N20-N19)/N19*100)</f>
+        <v>-19.9586349534643</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -29751,6 +30017,18 @@
         <f>'Raw data'!JT21</f>
         <v>1732</v>
       </c>
+      <c r="S21" s="6">
+        <f>IF(OR(L21="",L20=""),"",(L21-L20)/L20*100)</f>
+        <v>-12.6874349715405</v>
+      </c>
+      <c r="T21" s="6">
+        <f>IF(OR(M21="",M20=""),"",(M21-M20)/M20*100)</f>
+        <v>14.6902654867257</v>
+      </c>
+      <c r="U21" s="6">
+        <f>IF(OR(N21="",N20=""),"",(N21-N20)/N20*100)</f>
+        <v>-7.2093023255814</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -29820,6 +30098,18 @@
         <f>'Raw data'!KK21</f>
         <v>1759</v>
       </c>
+      <c r="S22" s="6">
+        <f>IF(OR(L22="",L21=""),"",(L22-L21)/L21*100)</f>
+        <v>-8.75508201317819</v>
+      </c>
+      <c r="T22" s="6">
+        <f>IF(OR(M22="",M21=""),"",(M22-M21)/M21*100)</f>
+        <v>-10.108024691358</v>
+      </c>
+      <c r="U22" s="6">
+        <f>IF(OR(N22="",N21=""),"",(N22-N21)/N21*100)</f>
+        <v>-0.417710944026734</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -29889,6 +30179,18 @@
         <f>'Raw data'!LB21</f>
         <v>1238</v>
       </c>
+      <c r="S23" s="6">
+        <f>IF(OR(L23="",L22=""),"",(L23-L22)/L22*100)</f>
+        <v>12.9215641084735</v>
+      </c>
+      <c r="T23" s="6">
+        <f>IF(OR(M23="",M22=""),"",(M23-M22)/M22*100)</f>
+        <v>9.72818311874106</v>
+      </c>
+      <c r="U23" s="6">
+        <f>IF(OR(N23="",N22=""),"",(N23-N22)/N22*100)</f>
+        <v>11.6331096196868</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -29958,6 +30260,18 @@
         <f>'Raw data'!LS21</f>
         <v>1803</v>
       </c>
+      <c r="S24" s="6">
+        <f>IF(OR(L24="",L23=""),"",(L24-L23)/L23*100)</f>
+        <v>5.59221715762977</v>
+      </c>
+      <c r="T24" s="6">
+        <f>IF(OR(M24="",M23=""),"",(M24-M23)/M23*100)</f>
+        <v>2.42503259452412</v>
+      </c>
+      <c r="U24" s="6">
+        <f>IF(OR(N24="",N23=""),"",(N24-N23)/N23*100)</f>
+        <v>13.2264529058116</v>
+      </c>
     </row>
     <row r="26" ht="32" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -29984,7 +30298,376 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>보고서 결과해석에 인용한 추가 계산 (모두 수식)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>해당 연도</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>계산 방법</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="n"/>
+      <c r="I29" s="9" t="n"/>
+      <c r="J29" s="10" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>재배면적 최소값(ha)</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="n"/>
+      <c r="C30" s="12" t="n"/>
+      <c r="D30" s="12" t="n"/>
+      <c r="E30" s="5">
+        <f>MIN($B$5:$B$24)</f>
+        <v>20088</v>
+      </c>
+      <c r="F30" s="4">
+        <f>INDEX($A$5:$A$24,MATCH(E30,$B$5:$B$24,0))</f>
+        <v>2022</v>
+      </c>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
+          <t>MIN(재배면적), 연도는 INDEX·MATCH</t>
+        </is>
+      </c>
+      <c r="H30" s="12" t="n"/>
+      <c r="I30" s="12" t="n"/>
+      <c r="J30" s="12" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>단수 최대값(kg/10a)</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="n"/>
+      <c r="C31" s="12" t="n"/>
+      <c r="D31" s="12" t="n"/>
+      <c r="E31" s="5">
+        <f>MAX($C$5:$C$24)</f>
+        <v>2943</v>
+      </c>
+      <c r="F31" s="4">
+        <f>INDEX($A$5:$A$24,MATCH(E31,$C$5:$C$24,0))</f>
+        <v>2008</v>
+      </c>
+      <c r="G31" s="11" t="inlineStr">
+        <is>
+          <t>MAX(단수)</t>
+        </is>
+      </c>
+      <c r="H31" s="12" t="n"/>
+      <c r="I31" s="12" t="n"/>
+      <c r="J31" s="12" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>총생산량 최소값(톤)</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="n"/>
+      <c r="C32" s="12" t="n"/>
+      <c r="D32" s="12" t="n"/>
+      <c r="E32" s="5">
+        <f>MIN($D$5:$D$24)</f>
+        <v>466755</v>
+      </c>
+      <c r="F32" s="4">
+        <f>INDEX($A$5:$A$24,MATCH(E32,$D$5:$D$24,0))</f>
+        <v>2017</v>
+      </c>
+      <c r="G32" s="11" t="inlineStr">
+        <is>
+          <t>MIN(총생산량)</t>
+        </is>
+      </c>
+      <c r="H32" s="12" t="n"/>
+      <c r="I32" s="12" t="n"/>
+      <c r="J32" s="12" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>일반봄감자 단수 최소값(kg/10a)</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="n"/>
+      <c r="C33" s="12" t="n"/>
+      <c r="D33" s="12" t="n"/>
+      <c r="E33" s="5">
+        <f>MIN($O$5:$O$24)</f>
+        <v>2152</v>
+      </c>
+      <c r="F33" s="4">
+        <f>INDEX($A$5:$A$24,MATCH(E33,$O$5:$O$24,0))</f>
+        <v>2017</v>
+      </c>
+      <c r="G33" s="11" t="inlineStr">
+        <is>
+          <t>MIN(일반봄감자 단수, O열)</t>
+        </is>
+      </c>
+      <c r="H33" s="12" t="n"/>
+      <c r="I33" s="12" t="n"/>
+      <c r="J33" s="12" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>전국 재배면적 감소량(ha)</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="n"/>
+      <c r="C34" s="12" t="n"/>
+      <c r="D34" s="12" t="n"/>
+      <c r="E34" s="5">
+        <f>B5-INDEX($B$5:$B$24,COUNT($D$5:$D$24))</f>
+        <v>8759</v>
+      </c>
+      <c r="F34" s="4" t="str">
+        <f>A5&amp;"→"&amp;INDEX($A$5:$A$24,COUNT($D$5:$D$24))</f>
+        <v>2005→2024</v>
+      </c>
+      <c r="G34" s="11" t="inlineStr">
+        <is>
+          <t>시작연도 값 − 최종연도 값</t>
+        </is>
+      </c>
+      <c r="H34" s="12" t="n"/>
+      <c r="I34" s="12" t="n"/>
+      <c r="J34" s="12" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>제주 재배면적 감소량(ha)</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="n"/>
+      <c r="C35" s="12" t="n"/>
+      <c r="D35" s="12" t="n"/>
+      <c r="E35" s="5">
+        <f>R5-INDEX($R$5:$R$24,COUNT($D$5:$D$24))</f>
+        <v>4371</v>
+      </c>
+      <c r="F35" s="4" t="str">
+        <f>A5&amp;"→"&amp;INDEX($A$5:$A$24,COUNT($D$5:$D$24))</f>
+        <v>2005→2024</v>
+      </c>
+      <c r="G35" s="11" t="inlineStr">
+        <is>
+          <t>시작연도 값 − 최종연도 값 (R열, 제주)</t>
+        </is>
+      </c>
+      <c r="H35" s="12" t="n"/>
+      <c r="I35" s="12" t="n"/>
+      <c r="J35" s="12" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>제주 감소량 ÷ 전국 감소량(%)</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="n"/>
+      <c r="C36" s="12" t="n"/>
+      <c r="D36" s="12" t="n"/>
+      <c r="E36" s="6">
+        <f>E35/E34*100</f>
+        <v>49.9029569585569</v>
+      </c>
+      <c r="F36" s="4" t="str">
+        <f>A5&amp;"→"&amp;INDEX($A$5:$A$24,COUNT($D$5:$D$24))</f>
+        <v>2005→2024</v>
+      </c>
+      <c r="G36" s="11" t="inlineStr">
+        <is>
+          <t>제주 감소량 ÷ 전국 감소량 × 100</t>
+        </is>
+      </c>
+      <c r="H36" s="12" t="n"/>
+      <c r="I36" s="12" t="n"/>
+      <c r="J36" s="12" t="n"/>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>최종연도 면적으로 시작연도 생산량을 내는 데 필요한 단수(kg/10a)</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="n"/>
+      <c r="C37" s="12" t="n"/>
+      <c r="D37" s="12" t="n"/>
+      <c r="E37" s="5">
+        <f>D5/INDEX($B$5:$B$24,COUNT($D$5:$D$24))*100</f>
+        <v>3730.71467311945</v>
+      </c>
+      <c r="F37" s="4" t="str">
+        <f>A5&amp;"→"&amp;INDEX($A$5:$A$24,COUNT($D$5:$D$24))</f>
+        <v>2005→2024</v>
+      </c>
+      <c r="G37" s="11" t="inlineStr">
+        <is>
+          <t>시작연도 생산량(톤)×1000 ÷ (최종연도 면적(ha)×10)</t>
+        </is>
+      </c>
+      <c r="H37" s="12" t="n"/>
+      <c r="I37" s="12" t="n"/>
+      <c r="J37" s="12" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>필요 단수가 단수 최대값보다 높은 비율(%)</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="n"/>
+      <c r="C38" s="12" t="n"/>
+      <c r="D38" s="12" t="n"/>
+      <c r="E38" s="6">
+        <f>(E37/E31-1)*100</f>
+        <v>26.7657041494885</v>
+      </c>
+      <c r="F38" s="4" t="n"/>
+      <c r="G38" s="11" t="inlineStr">
+        <is>
+          <t>(필요 단수 ÷ 단수 최대값 − 1) × 100</t>
+        </is>
+      </c>
+      <c r="H38" s="12" t="n"/>
+      <c r="I38" s="12" t="n"/>
+      <c r="J38" s="12" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>일반봄감자 재배면적 전년 대비 변화율(%)</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="n"/>
+      <c r="C39" s="12" t="n"/>
+      <c r="D39" s="12" t="n"/>
+      <c r="E39" s="6">
+        <f>INDEX($S$5:$S$24,MATCH(F39,$A$5:$A$24,0))</f>
+        <v>-25.3306713251809</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>2006</v>
+      </c>
+      <c r="G39" s="11" t="inlineStr">
+        <is>
+          <t>S열(전년 대비 변화율)에서 해당 연도 값</t>
+        </is>
+      </c>
+      <c r="H39" s="12" t="n"/>
+      <c r="I39" s="12" t="n"/>
+      <c r="J39" s="12" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>가을감자 재배면적 전년 대비 변화율(%)</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="n"/>
+      <c r="C40" s="12" t="n"/>
+      <c r="D40" s="12" t="n"/>
+      <c r="E40" s="6">
+        <f>INDEX($U$5:$U$24,MATCH(F40,$A$5:$A$24,0))</f>
+        <v>-39.5040924410207</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>2006</v>
+      </c>
+      <c r="G40" s="11" t="inlineStr">
+        <is>
+          <t>U열(전년 대비 변화율)에서 해당 연도 값</t>
+        </is>
+      </c>
+      <c r="H40" s="12" t="n"/>
+      <c r="I40" s="12" t="n"/>
+      <c r="J40" s="12" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>가을감자 재배면적 전년 대비 변화율(%)</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="n"/>
+      <c r="C41" s="12" t="n"/>
+      <c r="D41" s="12" t="n"/>
+      <c r="E41" s="6">
+        <f>INDEX($U$5:$U$24,MATCH(F41,$A$5:$A$24,0))</f>
+        <v>-19.043659043659</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>2011</v>
+      </c>
+      <c r="G41" s="11" t="inlineStr">
+        <is>
+          <t>U열(전년 대비 변화율)에서 해당 연도 값</t>
+        </is>
+      </c>
+      <c r="H41" s="12" t="n"/>
+      <c r="I41" s="12" t="n"/>
+      <c r="J41" s="12" t="n"/>
+    </row>
   </sheetData>
+  <mergeCells count="26">
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="G35:J35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="G29:J29"/>
+    <mergeCell ref="G41:J41"/>
+    <mergeCell ref="G32:J32"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="G40:J40"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="G31:J31"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="G36:J36"/>
+    <mergeCell ref="G39:J39"/>
+    <mergeCell ref="G38:J38"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="G37:J37"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="G34:J34"/>
+    <mergeCell ref="G30:J30"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="G33:J33"/>
+    <mergeCell ref="A32:D32"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -30020,23 +30703,23 @@
           <t>구분</t>
         </is>
       </c>
-      <c r="B3" s="9">
+      <c r="B3" s="13">
         <f>분석!A5</f>
         <v>2005</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="13">
         <f>B3+5</f>
         <v>2010</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="13">
         <f>C3+5</f>
         <v>2015</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="13">
         <f>D3+5</f>
         <v>2020</v>
       </c>
-      <c r="F3" s="9">
+      <c r="F3" s="13">
         <f>INDEX(분석!A5:A24,COUNT(분석!D5:D24))</f>
         <v>2024</v>
       </c>
